--- a/税案通报数据.xlsx
+++ b/税案通报数据.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="独立案件" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="金额明细" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'独立案件'!$A$3:$L$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'独立案件'!$A$3:$N$300</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +45,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +56,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001a1a2e"/>
         <bgColor rgb="001a1a2e"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
+        <bgColor rgb="00E8F0FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+        <bgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF7E0"/>
+        <bgColor rgb="00FEF7E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -99,8 +117,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L300"/>
+  <dimension ref="A1:N300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -478,9 +508,11 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -493,7 +525,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>297 条 | 2021—2026 | 数据来源：chinatax.gov.cn | 保留有金额、多维度的记录</t>
+          <t>297 条 | 2021—2026 | 金额单位：万元</t>
         </is>
       </c>
     </row>
@@ -545,15 +577,25 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>金额(万元)</t>
+          <t>追缴税款(万)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>摘要</t>
+          <t>罚款(万)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>滞纳金(万)</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>合计(万)</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -573,7 +615,7 @@
           <t>国家税务总局宿迁市税务局稽查局依法查处自然人王建军偷税案件</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -595,15 +637,15 @@
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="6" t="n">
         <v>81.14</v>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局宿迁市税务局稽查局依法查处自然人王建军偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", websi</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="6" t="n">
+        <v>162.33</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5250170/content.html</t>
         </is>
@@ -623,7 +665,7 @@
           <t>国家税务总局三明市税务局稽查局依法查处自然人王元春、王逢春偷税案件</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -645,15 +687,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="6" t="n">
         <v>298.29</v>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局三明市税务局稽查局依法查处自然人王元春、王逢春偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", w</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5250168/content.html</t>
         </is>
@@ -673,7 +713,7 @@
           <t>热门口腔医院隐匿千万收入偷税被罚——揭秘自然人郭宝山偷税案</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -697,7 +737,9 @@
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5250167/content.html</t>
         </is>
@@ -717,7 +759,7 @@
           <t>个人独资企业背后的偷税猫腻——揭秘自然人党迎凤偷税案</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -741,7 +783,9 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5250165/content.html</t>
         </is>
@@ -761,7 +805,7 @@
           <t>国家税务总局大连市税务局第三稽查局依法查处自然人王充少缴税款案件</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -783,15 +827,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="6" t="n">
         <v>116.61</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局大连市税务局第三稽查局依法查处自然人王充少缴税款案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", we</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5250162/content.html</t>
         </is>
@@ -811,7 +853,7 @@
           <t>煤款暗流：藏在私人账户里的偷税真相——揭秘内蒙古伊东集团西乌素煤炭有限责任公司私户收款偷税案件</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -843,7 +885,9 @@
       </c>
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249873/content.html</t>
         </is>
@@ -863,7 +907,7 @@
           <t>火爆直播间背后的私户收款真相——揭秘即墨区瑞安转角服装店私户收款偷税案</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -891,7 +935,9 @@
       </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249871/content.html</t>
         </is>
@@ -911,7 +957,7 @@
           <t>“私户”藏货款 “借款”作伪装——揭秘大柴旦和信科技有限公司私户收款偷税真相</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -935,7 +981,9 @@
       </c>
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249869/content.html</t>
         </is>
@@ -955,7 +1003,7 @@
           <t>营养食品公司的“隐身账”——揭秘湖南婴商营养食品有限公司私户收款偷税真相</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -983,7 +1031,9 @@
       </c>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249867/content.html</t>
         </is>
@@ -1003,7 +1053,7 @@
           <t>家装业务亿元账外收入的“隐身术”——揭秘秦皇岛城市人家装饰工程有限公司私户收款偷税真相</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1027,7 +1077,9 @@
       </c>
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249864/content.html</t>
         </is>
@@ -1047,7 +1099,7 @@
           <t>口腔诊所的“数字化”两本账——揭秘沈阳国民口腔门诊部有限公司私户收款偷税案</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1075,7 +1127,9 @@
       </c>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249862/content.html</t>
         </is>
@@ -1095,7 +1149,7 @@
           <t>大额流水背后的偷税“猫腻”——还原阿克苏启善建材有限公司私户收款偷税案件</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1123,7 +1177,9 @@
       </c>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249860/content.html</t>
         </is>
@@ -1143,7 +1199,7 @@
           <t>私户收款藏猫腻 “隐身”油款终现形——揭开泽州县郊南加油站隐匿收入偷税真相</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1167,7 +1223,9 @@
       </c>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249858/content.html</t>
         </is>
@@ -1187,7 +1245,7 @@
           <t>“百万学员”知识主播的偷税真相 ——揭秘“网上售课”主播王仲焘偷税案</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1211,7 +1269,9 @@
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249755/content.html</t>
         </is>
@@ -1255,7 +1315,9 @@
       <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249368/content.html</t>
         </is>
@@ -1275,7 +1337,7 @@
           <t>医美公司的“整形”账簿——揭秘辽宁曙光整形外科医院有限公司私户收款隐匿收入偷税案</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1307,7 +1369,9 @@
       </c>
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249367/content.html</t>
         </is>
@@ -1327,7 +1391,7 @@
           <t>POS机收款全入私账 医美企业偷税难逃法网——揭秘贵州吴氏嘉美整形美容有限公司私户收款隐匿收入偷税案</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1359,7 +1423,9 @@
       </c>
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249365/content.html</t>
         </is>
@@ -1379,7 +1445,7 @@
           <t>“美丽”账本背后的真相——揭秘常州苏王医疗美容门诊部有限公司私户收款隐匿收入偷税案</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1407,7 +1473,9 @@
       </c>
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249363/content.html</t>
         </is>
@@ -1427,7 +1495,7 @@
           <t>“免税”做幌 “私账”收款——揭秘北京邦定美容整形外科门诊部私户收款隐匿收入偷税案</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1459,7 +1527,9 @@
       </c>
       <c r="J22" s="4" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249360/content.html</t>
         </is>
@@ -1479,7 +1549,7 @@
           <t>藏不住的偷税账——揭秘保定华美整形美容医院有限公司私户收款隐匿收入偷税案</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1507,7 +1577,9 @@
       </c>
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249358/content.html</t>
         </is>
@@ -1527,7 +1599,7 @@
           <t>“账外账”里的千万营收——揭秘广州氧颜医疗美容门诊部有限公司私户收款隐匿收入偷税案</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1555,7 +1627,9 @@
       </c>
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249356/content.html</t>
         </is>
@@ -1575,7 +1649,7 @@
           <t>税务部门依法查处“探店”网红白冰偷税案件 税款、滞纳金、罚款1891万元已入库</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -1597,15 +1671,15 @@
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="6" t="n">
         <v>1891</v>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>税务部门依法查处“探店”网红白冰偷税案件 税款、滞纳金、罚款1891万元已入库_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinat</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="6" t="n">
+        <v>911.1799999999999</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249226/content.html</t>
         </is>
@@ -1625,7 +1699,7 @@
           <t>退税“馅饼”实为“陷阱” 近1800人上当受骗——咸阳税警联合依法查处一起诱导纳税人虚假填报个人所得税专项附加扣除骗取退税案件</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -1643,15 +1717,13 @@
       </c>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr"/>
-      <c r="J26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>退税“馅饼”实为“陷阱” 近1800人上当受骗——咸阳税警联合依法查处一起诱导纳税人虚假填报个人所得税专项附加扣除骗取退税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="6" t="n">
+        <v>1573.25</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249196/content.html</t>
         </is>
@@ -1671,7 +1743,7 @@
           <t>国家税务总局咸阳市税务局联合公安机关依法查处“黑中介”诱导纳税人虚假填报个人所得税专项附加扣除骗取退税案件</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -1689,15 +1761,13 @@
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局咸阳市税务局联合公安机关依法查处“黑中介”诱导纳税人虚假填报个人所得税专项附加扣除骗取退税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", website</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="6" t="n">
+        <v>1573.25</v>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5249195/content.html</t>
         </is>
@@ -1717,7 +1787,7 @@
           <t>“绕行”万里偷逃消费税的黄金首饰——揭秘辽宁潮尊珠宝销售有限责任公司偷逃消费税案件</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1745,7 +1815,9 @@
       </c>
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248985/content.html</t>
         </is>
@@ -1765,7 +1837,7 @@
           <t>六店隐匿藏私账  法网恢恢终追责——揭开靖江靖祥珠宝有限公司偷逃消费税案真相</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1789,7 +1861,9 @@
       </c>
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248983/content.html</t>
         </is>
@@ -1809,7 +1883,7 @@
           <t>隐匿千万营收 注销难逃追责——揭秘歙县4家珠宝店业主林浩、林海偷逃消费税案件</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1833,7 +1907,9 @@
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248981/content.html</t>
         </is>
@@ -1853,7 +1929,7 @@
           <t>私人账户收货款 隐匿收入终被查——揭秘汶上县鑫福黄金珠宝店偷逃消费税案件</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1877,7 +1953,9 @@
       </c>
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248979/content.html</t>
         </is>
@@ -1897,7 +1975,7 @@
           <t>隐藏起来的黄金销售款——揭秘西藏垦泰商贸两家成都分公司偷逃消费税案件</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -1925,7 +2003,9 @@
       </c>
       <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248977/content.html</t>
         </is>
@@ -1945,7 +2025,7 @@
           <t>国家税务总局成都市税务局第三稽查局依法查处西藏垦泰商贸有限公司两家成都分公司偷逃黄金首饰消费税案件</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -1971,15 +2051,13 @@
           <t>西藏垦泰商贸有限公司</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="6" t="n">
         <v>277.19</v>
       </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局成都市税务局第三稽查局依法查处西藏垦泰商贸有限公司两家成都分公司偷逃黄金首饰消费税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248976/content.html</t>
         </is>
@@ -1999,7 +2077,7 @@
           <t>私人账户成隐秘“金库”——还原阿克苏市富晨珠宝行偷逃消费税案始末</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2023,7 +2101,9 @@
       </c>
       <c r="J34" s="4" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248975/content.html</t>
         </is>
@@ -2043,7 +2123,7 @@
           <t>A级光环下的“影子账户”——揭秘贵州省仁怀市茅台镇鹏程酒厂偷逃消费税案件</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2071,7 +2151,9 @@
       </c>
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr"/>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248973/content.html</t>
         </is>
@@ -2091,7 +2173,7 @@
           <t>石化经销企业暗藏的油品“调和术”——还原茂名市宏坚石化有限公司偷逃消费税案件真相</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2115,7 +2197,9 @@
       </c>
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248971/content.html</t>
         </is>
@@ -2135,7 +2219,7 @@
           <t>税务部门曝光4起社会教育培训行业偷税案件 私账收款、少计收入、骗享优惠等违法行为被依法查处</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -2157,15 +2241,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="6" t="n">
         <v>24000</v>
       </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>税务部门曝光4起社会教育培训行业偷税案件 私账收款、少计收入、骗享优惠等违法行为被依法查处_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248811/content.html</t>
         </is>
@@ -2205,7 +2287,9 @@
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248810/content.html</t>
         </is>
@@ -2225,7 +2309,7 @@
           <t>账外收入藏偷税迷局——揭秘重庆市江北区金标尺职业考试培训有限公司偷税真相</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2253,7 +2337,9 @@
       </c>
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248808/content.html</t>
         </is>
@@ -2273,7 +2359,7 @@
           <t>收进来的学费  “调”低了的利润——揭秘铜仁市红色二八职业技术培训学校有限公司骗享税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2301,7 +2387,9 @@
       </c>
       <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248806/content.html</t>
         </is>
@@ -2321,7 +2409,7 @@
           <t>“不确认收入”背后的偷税算计——揭秘宁夏易阳教育咨询有限公司少计收入偷税案件</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2353,7 +2441,9 @@
       </c>
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248804/content.html</t>
         </is>
@@ -2373,7 +2463,7 @@
           <t>学费流入“私账” 偷税终食苦果——揭秘山东正心教育科技有限公司偷税案件</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2405,7 +2495,9 @@
       </c>
       <c r="J42" s="4" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248802/content.html</t>
         </is>
@@ -2425,7 +2517,7 @@
           <t>税务部门曝光4起骗取出口退税违法案件 “买单配票”、虚构交易等骗税行为均被依法查处</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -2443,15 +2535,11 @@
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="n">
-        <v>20100</v>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>税务部门曝光4起骗取出口退税违法案件 “买单配票”、虚构交易等骗税行为均被依法查处_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chin</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247878/content.html</t>
         </is>
@@ -2471,7 +2559,7 @@
           <t>天津市税务局第一稽查局联合公安机关依法查处以陈明雄为首的犯罪团伙虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -2498,12 +2586,10 @@
       </c>
       <c r="I44" s="4" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>天津市税务局第一稽查局联合公安机关依法查处以陈明雄为首的犯罪团伙虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chin</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248605/content.html</t>
         </is>
@@ -2523,7 +2609,7 @@
           <t>假厂房、旧设备、“真”发票？——揭秘陕西省卓拓物资回收再生利用有限公司</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2551,7 +2637,9 @@
       </c>
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248604/content.html</t>
         </is>
@@ -2599,7 +2687,9 @@
       </c>
       <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248602/content.html</t>
         </is>
@@ -2619,7 +2709,7 @@
           <t>酸枣仁背后的“无本买卖”——揭开内丘一色秋水中药材有限公司等8户企业虚开增值税发票案真相</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2643,7 +2733,9 @@
       </c>
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5248600/content.html</t>
         </is>
@@ -2683,7 +2775,9 @@
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247877/content.html</t>
         </is>
@@ -2703,7 +2797,7 @@
           <t>天津市税务公安等部门联合依法查处以杨荣栋为实际控制人的3户企业骗取出口退税案件</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -2730,12 +2824,10 @@
       </c>
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>天津市税务公安等部门联合依法查处以杨荣栋为实际控制人的3户企业骗取出口退税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinat</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247875/content.html</t>
         </is>
@@ -2755,7 +2847,7 @@
           <t>农产品发票成“道具” 天价香菇液的骗税迷局——揭开赤水汇达丰商贸有限公司骗取出口退税案件真相</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2779,7 +2871,9 @@
       </c>
       <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247872/content.html</t>
         </is>
@@ -2799,7 +2893,7 @@
           <t>空壳企业搭桥 跨境出口假象下的退税骗局——揭开泓一生物工程（重庆）有限公司骗取出口退税案件真相</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2827,7 +2921,9 @@
       </c>
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247870/content.html</t>
         </is>
@@ -2847,7 +2943,7 @@
           <t>千万“假研发”费用背后的骗享操作——揭秘西藏慧业医药科技有限公司骗享税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2879,7 +2975,9 @@
       </c>
       <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247591/content.html</t>
         </is>
@@ -2899,7 +2997,7 @@
           <t>25个账户打款的背后……——揭秘扬州春风船舶机械制造有限公司骗享税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2927,7 +3025,9 @@
       </c>
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr"/>
-      <c r="L53" s="4" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247588/content.html</t>
         </is>
@@ -2947,7 +3047,7 @@
           <t>千万收入隐“云端”——揭秘安徽星印网络科技有限公司骗享税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -2979,7 +3079,9 @@
       </c>
       <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247586/content.html</t>
         </is>
@@ -2999,7 +3101,7 @@
           <t>压利润“扮小微” 骗享优惠终被查——揭秘嘉峪关宏兴西域能源有限责任公司骗享税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3027,7 +3129,9 @@
       </c>
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5247583/content.html</t>
         </is>
@@ -3047,7 +3151,7 @@
           <t>依法查处网红偷逃税行为 系统施治促进持续健康发展</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3070,12 +3174,10 @@
       </c>
       <c r="I56" s="4" t="inlineStr"/>
       <c r="J56" s="4" t="inlineStr"/>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>依法查处网红偷逃税行为 系统施治促进持续健康发展_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", websiteNam</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246910/content.html</t>
         </is>
@@ -3095,7 +3197,7 @@
           <t>国家税务总局重庆市税务局第三稽查局依法查处网络主播彭煊之偷税案件</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3121,15 +3223,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="4" t="n">
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="6" t="n">
         <v>216.32</v>
       </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局重庆市税务局第三稽查局依法查处网络主播彭煊之偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", we</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246904/content.html</t>
         </is>
@@ -3149,7 +3249,7 @@
           <t>佣金收入虚假申报 侥幸偷税终被处罚——揭秘网络主播杨遂娃偷税案</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3173,7 +3273,9 @@
       <c r="I58" s="4" t="inlineStr"/>
       <c r="J58" s="4" t="inlineStr"/>
       <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246903/content.html</t>
         </is>
@@ -3193,7 +3295,7 @@
           <t>货运司机冒充研发人员 “高新”招牌下的偷梁换柱——揭秘涉税中介沈阳遇知科技服务有限公司及其实际控制人徐驰帮助所代理企业虚假申报高新技术企业资格造成少缴税款案件</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3217,7 +3319,9 @@
       <c r="I59" s="4" t="inlineStr"/>
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246677/content.html</t>
         </is>
@@ -3237,7 +3341,7 @@
           <t>国家税务总局沈阳市税务局第一稽查局联合公安机关依法查处涉税中介沈阳遇知科技服务有限公司及其实际控制人徐驰帮助所代理企业虚假申报高新技术企业资格造成少缴税款案件</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3263,15 +3367,13 @@
           <t>沈阳遇知科技服务有限公司</t>
         </is>
       </c>
-      <c r="J60" s="4" t="n">
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="6" t="n">
         <v>233.99</v>
       </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局沈阳市税务局第一稽查局联合公安机关依法查处涉税中介沈阳遇知科技服务有限公司及其实际控制人徐驰帮助所代理企业虚假申报高新技术企业资格造成少缴税款案件_国家税务总局 var websiteId = "a52dee227d764e87</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="N60" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246676/content.html</t>
         </is>
@@ -3291,7 +3393,7 @@
           <t>大额“服务费”背后的虚开真相——揭秘宜兴市苏瑞代理记帐有限公司及其实际控制人钱文革帮助所代理企业虚列成本造成少缴税款案件</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3319,7 +3421,9 @@
       </c>
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246671/content.html</t>
         </is>
@@ -3339,7 +3443,7 @@
           <t>藏在“天价”顾问费里的“生财之道”——揭秘涉税中介宁波甬九财税服务有限公司及其实际控制人凌珊帮助所代理企业虚列成本导致少缴税款案件</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3363,7 +3467,9 @@
       <c r="I62" s="4" t="inlineStr"/>
       <c r="J62" s="4" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246669/content.html</t>
         </is>
@@ -3383,7 +3489,7 @@
           <t>国家税务总局宁波市税务局稽查局依法查处涉税中介宁波甬九财税服务有限公司及其实际控制人凌珊帮助所代理企业虚列成本导致少缴税款案件</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3409,15 +3515,17 @@
           <t>宁波甬九财税服务有限公司</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="J63" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局宁波市税务局稽查局依法查处涉税中介宁波甬九财税服务有限公司及其实际控制人凌珊帮助所代理企业虚列成本导致少缴税款案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="K63" s="6" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="L63" s="4" t="inlineStr"/>
+      <c r="M63" s="6" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246667/content.html</t>
         </is>
@@ -3437,7 +3545,7 @@
           <t>涉税“黑中介”的虚开“流水线”——揭秘涉税中介吉林市弘成财务咨询服务有限公司及其实际控制人李丽等人虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3465,7 +3573,9 @@
       <c r="I64" s="4" t="inlineStr"/>
       <c r="J64" s="4" t="inlineStr"/>
       <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr"/>
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246666/content.html</t>
         </is>
@@ -3485,7 +3595,7 @@
           <t>国家税务总局吉林市税务局稽查局联合公安机关依法查处涉税中介吉林市弘成财务咨询服务有限公司及其实际控制人李丽等人虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3515,15 +3625,13 @@
           <t>吉林市弘成财务咨询服务有限公司</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局吉林市税务局稽查局联合公安机关依法查处涉税中介吉林市弘成财务咨询服务有限公司及其实际控制人李丽等人虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab1</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246665/content.html</t>
         </is>
@@ -3543,7 +3651,7 @@
           <t>触碰红线的“税务代理”——揭秘涉税中介广元市铭慧企业管理有限公司虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3563,7 +3671,9 @@
       <c r="I66" s="4" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246664/content.html</t>
         </is>
@@ -3583,7 +3693,7 @@
           <t>国家税务总局广元市税务局稽查局联合公安机关依法查处涉税中介广元市铭慧企业管理有限公司及其实际控制人梁洪铭虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3609,15 +3719,13 @@
           <t>广元市铭慧企业管理有限公司</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="6" t="n">
         <v>24.5</v>
       </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局广元市税务局稽查局联合公安机关依法查处涉税中介广元市铭慧企业管理有限公司及其实际控制人梁洪铭虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14",</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246663/content.html</t>
         </is>
@@ -3637,7 +3745,7 @@
           <t>涉税中介操控“空壳企业” 上下游勾连暗做“开票生意”——揭秘涉税中介商洛卡尔曼企业管理咨询服务有限公司及其实际控制人黄祖宾虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3661,7 +3769,9 @@
       <c r="I68" s="4" t="inlineStr"/>
       <c r="J68" s="4" t="inlineStr"/>
       <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246662/content.html</t>
         </is>
@@ -3681,7 +3791,7 @@
           <t>国家税务总局商洛市税务局稽查局依法查处涉税中介商洛卡尔曼企业管理咨询服务有限公司及其实际控制人黄祖宾虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3707,15 +3817,11 @@
           <t>商洛卡尔曼企业管理咨询服务有限公司</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n">
-        <v>6952.35</v>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局商洛市税务局稽查局依法查处涉税中介商洛卡尔曼企业管理咨询服务有限公司及其实际控制人黄祖宾虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", w</t>
-        </is>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246661/content.html</t>
         </is>
@@ -3755,7 +3861,9 @@
       <c r="I70" s="4" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246255/content.html</t>
         </is>
@@ -3775,7 +3883,7 @@
           <t>“借壳出口”隐匿收入  逃避缴纳税款被处罚——揭秘合源（湖北）纳米技术产业有限公司隐匿出口应征税货物收入偷税案件</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -3807,7 +3915,9 @@
       </c>
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246254/content.html</t>
         </is>
@@ -3851,7 +3961,9 @@
       <c r="I72" s="4" t="inlineStr"/>
       <c r="J72" s="4" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr"/>
-      <c r="L72" s="4" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246252/content.html</t>
         </is>
@@ -3871,7 +3983,7 @@
           <t>国家税务总局邯郸市税务局稽查局依法查处邯郸市丛台区群帮耐火材料厂隐匿出口应征税货物收入偷税案件</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3897,15 +4009,13 @@
           <t>邯郸市丛台区群帮耐火材料厂</t>
         </is>
       </c>
-      <c r="J73" s="4" t="n">
-        <v>328.08</v>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局邯郸市税务局稽查局依法查处邯郸市丛台区群帮耐火材料厂隐匿出口应征税货物收入偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode =</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="6" t="n">
+        <v>550.91</v>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246251/content.html</t>
         </is>
@@ -3925,7 +4035,7 @@
           <t>国家税务总局福州市税务局第二稽查局依法查处福州晋安区德乐加乐贸易有限公司拒不申报出口货物应征税偷税案件</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -3951,15 +4061,13 @@
           <t>福州晋安区德乐加乐贸易有限公司</t>
         </is>
       </c>
-      <c r="J74" s="4" t="n">
-        <v>202.37</v>
-      </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局福州市税务局第二稽查局依法查处福州晋安区德乐加乐贸易有限公司拒不申报出口货物应征税偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCo</t>
-        </is>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr"/>
+      <c r="L74" s="4" t="inlineStr"/>
+      <c r="M74" s="6" t="n">
+        <v>402.28</v>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246248/content.html</t>
         </is>
@@ -3979,7 +4087,7 @@
           <t>国家税务总局佛山市税务局第一稽查局依法查处佛山海中金进出口有限公司虚假申报出口应征税货物收入偷税案件</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4005,15 +4113,13 @@
           <t>佛山海中金进出口有限公司</t>
         </is>
       </c>
-      <c r="J75" s="4" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局佛山市税务局第一稽查局依法查处佛山海中金进出口有限公司虚假申报出口应征税货物收入偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCod</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr"/>
+      <c r="M75" s="6" t="n">
+        <v>125.24</v>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5246246/content.html</t>
         </is>
@@ -4033,7 +4139,7 @@
           <t>神秘失踪的服务费——揭秘网络交易平台浙江嫲嫲团网络科技有限公司涉税违法案</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4061,7 +4167,9 @@
       </c>
       <c r="J76" s="4" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr"/>
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245808/content.html</t>
         </is>
@@ -4081,7 +4189,7 @@
           <t>货运平台数亿运费背后的“发票生意”——揭秘网络货运平台运是滴科技发展有限责任公司虚开增值税专用发票案</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4105,7 +4213,9 @@
       </c>
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="L77" s="4" t="inlineStr"/>
+      <c r="M77" s="4" t="inlineStr"/>
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245806/content.html</t>
         </is>
@@ -4125,7 +4235,7 @@
           <t>国家税务总局西安市税务局第三稽查局联合公安机关依法查处网络货运平台运是滴科技发展有限责任公司虚开增值税专用发票案件</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4148,12 +4258,12 @@
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr"/>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局西安市税务局第三稽查局联合公安机关依法查处网络货运平台运是滴科技发展有限责任公司虚开增值税专用发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", web</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr"/>
+      <c r="M78" s="6" t="n">
+        <v>130400</v>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245805/content.html</t>
         </is>
@@ -4173,7 +4283,7 @@
           <t>“灵活用工”异化成“灵活虚开”——还原灵活用工平台辽宁合众易薪科技有限公司虚开发票案真相</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4201,7 +4311,9 @@
       </c>
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245804/content.html</t>
         </is>
@@ -4241,7 +4353,9 @@
       <c r="I80" s="4" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245382/content.html</t>
         </is>
@@ -4261,7 +4375,7 @@
           <t>千万成本违法扣除的隐身代理——揭秘涉税中介上海账一财税咨询有限公司操控空壳企业实施违法策划导致其代理企业少缴税款案件</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4289,7 +4403,9 @@
       <c r="I81" s="4" t="inlineStr"/>
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr"/>
-      <c r="L81" s="4" t="inlineStr">
+      <c r="L81" s="4" t="inlineStr"/>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245381/content.html</t>
         </is>
@@ -4309,7 +4425,7 @@
           <t>国家税务总局上海市税务局第一稽查局依法查处涉税中介上海账一财税咨询有限公司操控空壳企业实施违法策划导致其代理企业少缴税款案件</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4339,15 +4455,15 @@
           <t>上海账一财税咨询有限公司</t>
         </is>
       </c>
-      <c r="J82" s="4" t="n">
+      <c r="J82" s="6" t="n">
+        <v>484.39</v>
+      </c>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="6" t="n">
         <v>18.9</v>
       </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局上海市税务局第一稽查局依法查处涉税中介上海账一财税咨询有限公司操控空壳企业实施违法策划导致其代理企业少缴税款案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14"</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
+      <c r="N82" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245380/content.html</t>
         </is>
@@ -4367,7 +4483,7 @@
           <t>国家税务总局福州市税务局稽查局依法查处涉税中介福州金汇鑫财税咨询有限公司帮助其代理企业骗取出口退税案件</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4389,15 +4505,13 @@
           <t>福州金汇鑫财税咨询有限公司</t>
         </is>
       </c>
-      <c r="J83" s="4" t="n">
-        <v>1129.14</v>
-      </c>
-      <c r="K83" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局福州市税务局稽查局依法查处涉税中介福州金汇鑫财税咨询有限公司帮助其代理企业骗取出口退税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCo</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="6" t="n">
+        <v>564.5700000000001</v>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245378/content.html</t>
         </is>
@@ -4417,7 +4531,7 @@
           <t>涉税中介伪装“科技公司”暗做“偷税生意”——揭秘江西旺桐科技有限公司策划帮助灵活用工人员违规转换收入性质造成其少缴税款案件</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4449,7 +4563,9 @@
       </c>
       <c r="J84" s="4" t="inlineStr"/>
       <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr">
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245377/content.html</t>
         </is>
@@ -4469,7 +4585,7 @@
           <t>国家税务总局安顺市税务局稽查局依法查处涉税中介贵州理得清财务有限公司介绍虚开增值税专用发票造成其代理企业少缴税款案件</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4499,15 +4615,13 @@
           <t>贵州理得清财务有限公司</t>
         </is>
       </c>
-      <c r="J85" s="4" t="n">
+      <c r="J85" s="4" t="inlineStr"/>
+      <c r="K85" s="4" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr"/>
+      <c r="M85" s="6" t="n">
         <v>937.4</v>
       </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局安顺市税务局稽查局依法查处涉税中介贵州理得清财务有限公司介绍虚开增值税专用发票造成其代理企业少缴税款案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", we</t>
-        </is>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
+      <c r="N85" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245374/content.html</t>
         </is>
@@ -4527,7 +4641,7 @@
           <t>国家税务总局大连市税务局第一稽查局依法查处涉税中介大连市澎源财税管理咨询有限公司介绍虚开发票造成其代理企业少缴税款案件</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4553,15 +4667,13 @@
           <t>大连市澎源财税管理咨询有限公司</t>
         </is>
       </c>
-      <c r="J86" s="4" t="n">
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="6" t="n">
         <v>2736.04</v>
       </c>
-      <c r="K86" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局大连市税务局第一稽查局依法查处涉税中介大连市澎源财税管理咨询有限公司介绍虚开发票造成其代理企业少缴税款案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", w</t>
-        </is>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
+      <c r="N86" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245372/content.html</t>
         </is>
@@ -4581,7 +4693,7 @@
           <t>国家税务总局深圳市税务局稽查局依法查处涉税中介深圳市财智恒通企业管理咨询有限公司非法提供银行账户和发票导致其代理企业少缴税款案件</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4607,15 +4719,13 @@
           <t>深圳市财智恒通企业管理咨询有限公司</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n">
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="6" t="n">
         <v>4792.11</v>
       </c>
-      <c r="K87" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局深圳市税务局稽查局依法查处涉税中介深圳市财智恒通企业管理咨询有限公司非法提供银行账户和发票导致其代理企业少缴税款案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab1</t>
-        </is>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
+      <c r="N87" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245370/content.html</t>
         </is>
@@ -4635,7 +4745,7 @@
           <t>“黑中介”操控49户空壳企业的“黑买卖” ——揭秘涉税中介天津畅泽财务管理有限公司及其实际控制人张凤梅虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4663,7 +4773,9 @@
       <c r="I88" s="4" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr">
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr"/>
+      <c r="N88" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245369/content.html</t>
         </is>
@@ -4683,7 +4795,7 @@
           <t>天津税务部门联合公安机关依法查处涉税中介 天津畅泽财务管理有限公司及其实际控制人张凤梅虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4713,15 +4825,13 @@
           <t>天津畅泽财务管理有限公司</t>
         </is>
       </c>
-      <c r="J89" s="4" t="n">
+      <c r="J89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr"/>
+      <c r="M89" s="6" t="n">
         <v>16000</v>
       </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>天津税务部门联合公安机关依法查处涉税中介 天津畅泽财务管理有限公司及其实际控制人张凤梅虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteC</t>
-        </is>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
+      <c r="N89" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245368/content.html</t>
         </is>
@@ -4741,7 +4851,7 @@
           <t>五层虚开发票网络的“罪与罚” ——揭秘涉税中介涟源市娄涟财务管理有限公司及其实际控制人谢久华勾结税务人员虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4765,7 +4875,9 @@
       <c r="I90" s="4" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr"/>
-      <c r="L90" s="4" t="inlineStr">
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245367/content.html</t>
         </is>
@@ -4785,7 +4897,7 @@
           <t>湖南省娄底市税务部门联合公安机关依法查处涉税中介涟源市娄涟财务管理有限公司及其实际控制人谢久华勾结税务人员虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4815,15 +4927,13 @@
           <t>涟源市娄涟财务管理有限公司</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n">
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="6" t="n">
         <v>26000</v>
       </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>湖南省娄底市税务部门联合公安机关依法查处涉税中介涟源市娄涟财务管理有限公司及其实际控制人谢久华勾结税务人员虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14"</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
+      <c r="N91" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245366/content.html</t>
         </is>
@@ -4843,7 +4953,7 @@
           <t>“拆”出来的优惠 “分”出来的风险——揭露广西咕咕狗商务秘书有限公司利用关联企业拆分收入偷税真相</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -4871,7 +4981,9 @@
       </c>
       <c r="J92" s="4" t="inlineStr"/>
       <c r="K92" s="4" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr">
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr"/>
+      <c r="N92" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245025/content.html</t>
         </is>
@@ -4891,7 +5003,7 @@
           <t>国家税务总局安顺市税务局第一稽查局依法查处安顺市百年婚宴有限公司利用关联个体工商户拆分收入偷税案件</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4917,15 +5029,13 @@
           <t>安顺市百年婚宴有限公司</t>
         </is>
       </c>
-      <c r="J93" s="4" t="n">
-        <v>249.77</v>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局安顺市税务局第一稽查局依法查处安顺市百年婚宴有限公司利用关联个体工商户拆分收入偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="6" t="n">
+        <v>392.79</v>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245022/content.html</t>
         </is>
@@ -4945,7 +5055,7 @@
           <t>国家税务总局宁波市税务局第三稽查局依法查处夏安阳拆分收入骗享个人所得税税收优惠偷税案件</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -4967,15 +5077,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="n">
-        <v>345.92</v>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局宁波市税务局第三稽查局依法查处夏安阳拆分收入骗享个人所得税税收优惠偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "ch</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="6" t="n">
+        <v>518.88</v>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245020/content.html</t>
         </is>
@@ -4995,7 +5103,7 @@
           <t>扫码支付藏“私”账 骗享退税终被罚——还原遵化市千里行加油加气站骗取增值税留抵退税案件真相</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5019,7 +5127,9 @@
       </c>
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr">
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245019/content.html</t>
         </is>
@@ -5039,7 +5149,7 @@
           <t>“库存迷云”背后的退税骗局——揭开常州马丁新能源科技有限公司虚假申报骗取增值税留抵退税案件真相</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5063,7 +5173,9 @@
       </c>
       <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="4" t="inlineStr">
+      <c r="L96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245017/content.html</t>
         </is>
@@ -5083,7 +5195,7 @@
           <t>货款“隐身”入私户 虚增留抵设骗局——揭秘海南粤弘远轮胎贸易有限公司骗取增值税留抵退税案件</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5111,7 +5223,9 @@
       </c>
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="4" t="inlineStr">
+      <c r="L97" s="4" t="inlineStr"/>
+      <c r="M97" s="4" t="inlineStr"/>
+      <c r="N97" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5245015/content.html</t>
         </is>
@@ -5151,7 +5265,9 @@
       <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr"/>
       <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="4" t="inlineStr">
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244807/content.html</t>
         </is>
@@ -5171,7 +5287,7 @@
           <t>国家税务总局赤峰市税务局第一稽查局依法查处网络主播郭鑫鑫偷税案件</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -5193,15 +5309,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="4" t="n">
+      <c r="J99" s="4" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr"/>
+      <c r="L99" s="4" t="inlineStr"/>
+      <c r="M99" s="6" t="n">
         <v>141.01</v>
       </c>
-      <c r="K99" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局赤峰市税务局第一稽查局依法查处网络主播郭鑫鑫偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", we</t>
-        </is>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
+      <c r="N99" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244805/content.html</t>
         </is>
@@ -5221,7 +5335,7 @@
           <t>被戳穿的销售额“隐身术” ——揭秘吉林市昌邑区胖多大码服饰店平台销售偷税案件</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5253,7 +5367,9 @@
       </c>
       <c r="J100" s="4" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="4" t="inlineStr">
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244804/content.html</t>
         </is>
@@ -5273,7 +5389,7 @@
           <t>虚假“小规模”身份被识破 直播带货隐匿收入被查——揭秘哈尔滨红博商贸城女人世界网络店铺偷税案件</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5297,7 +5413,9 @@
       <c r="I101" s="4" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="4" t="inlineStr">
+      <c r="L101" s="4" t="inlineStr"/>
+      <c r="M101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244802/content.html</t>
         </is>
@@ -5317,7 +5435,7 @@
           <t>“隐形”的电商订单——揭开江苏常州以马内利塑业有限公司网店销售偷税案件真相</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5349,7 +5467,9 @@
       </c>
       <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="4" t="inlineStr">
+      <c r="L102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244800/content.html</t>
         </is>
@@ -5369,7 +5489,7 @@
           <t>国家税务总局常州市税务局第一稽查局依法查处常州以马内利塑业有限公司网店销售偷税案件</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -5395,15 +5515,13 @@
           <t>常州以马内利塑业有限公司</t>
         </is>
       </c>
-      <c r="J103" s="4" t="n">
+      <c r="J103" s="4" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr"/>
+      <c r="L103" s="4" t="inlineStr"/>
+      <c r="M103" s="6" t="n">
         <v>101.67</v>
       </c>
-      <c r="K103" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局第一稽查局依法查处常州以马内利塑业有限公司网店销售偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chin</t>
-        </is>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
+      <c r="N103" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244798/content.html</t>
         </is>
@@ -5423,7 +5541,7 @@
           <t>实体服装“小”店背后的线上偷税“大”案——揭秘南昌市东湖区上品屋服饰店线上销售偷税案件</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5451,7 +5569,9 @@
       </c>
       <c r="J104" s="4" t="inlineStr"/>
       <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr">
+      <c r="L104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244797/content.html</t>
         </is>
@@ -5471,7 +5591,7 @@
           <t>百万销量显繁荣  隐匿收入现原形——揭露青岛市南区尚品优食品店直播销售偷税真相</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5495,7 +5615,9 @@
       </c>
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr"/>
-      <c r="L105" s="4" t="inlineStr">
+      <c r="L105" s="4" t="inlineStr"/>
+      <c r="M105" s="4" t="inlineStr"/>
+      <c r="N105" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244795/content.html</t>
         </is>
@@ -5515,7 +5637,7 @@
           <t>国家税务总局青岛市税务局第一稽查局依法查处市南区尚品优食品店直播销售偷税案件</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -5541,15 +5663,13 @@
           <t>市南区尚品优食品店</t>
         </is>
       </c>
-      <c r="J106" s="4" t="n">
+      <c r="J106" s="4" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="6" t="n">
         <v>177.12</v>
       </c>
-      <c r="K106" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局青岛市税务局第一稽查局依法查处市南区尚品优食品店直播销售偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinata</t>
-        </is>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
+      <c r="N106" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5244794/content.html</t>
         </is>
@@ -5569,7 +5689,7 @@
           <t>无实物假交易 药企购姜背后藏骗局——揭秘贵州博方民族药业开发有限公司虚开农产品发票偷税案</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5601,7 +5721,9 @@
       </c>
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr"/>
-      <c r="L107" s="4" t="inlineStr">
+      <c r="L107" s="4" t="inlineStr"/>
+      <c r="M107" s="4" t="inlineStr"/>
+      <c r="N107" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243620/content.html</t>
         </is>
@@ -5621,7 +5743,7 @@
           <t>国家税务总局盘锦市税务局稽查局依法查处以戴元军为首的犯罪团伙虚开农产品发票骗取出口退税案件</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -5643,15 +5765,11 @@
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="4" t="n">
-        <v>1852.72</v>
-      </c>
-      <c r="K108" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局盘锦市税务局稽查局依法查处以戴元军为首的犯罪团伙虚开农产品发票骗取出口退税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "</t>
-        </is>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
+      <c r="J108" s="4" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243617/content.html</t>
         </is>
@@ -5671,7 +5789,7 @@
           <t>税务部门再曝光6起加油站偷税案件 依法查处隐匿收入偷税行为 坚决维护税收法治公平</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -5693,15 +5811,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="4" t="n">
+      <c r="J109" s="4" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+      <c r="M109" s="6" t="n">
         <v>294300</v>
       </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>税务部门再曝光6起加油站偷税案件 依法查处隐匿收入偷税行为 坚决维护税收法治公平_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "china</t>
-        </is>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
+      <c r="N109" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243437/content.html</t>
         </is>
@@ -5721,7 +5837,7 @@
           <t>加油收款“套路深”监控系统“藏猫腻”——还原德惠市天赐加油站隐匿收入偷税案件真相</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5749,7 +5865,9 @@
       </c>
       <c r="J110" s="4" t="inlineStr"/>
       <c r="K110" s="4" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243435/content.html</t>
         </is>
@@ -5789,7 +5907,9 @@
       <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr">
+      <c r="L111" s="4" t="inlineStr"/>
+      <c r="M111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243433/content.html</t>
         </is>
@@ -5809,7 +5929,7 @@
           <t>国家税务总局鹤壁市税务局稽查局依法查处鹤壁市国用商贸有限公司偷税案件</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -5835,15 +5955,13 @@
           <t>鹤壁市国用商贸有限公司</t>
         </is>
       </c>
-      <c r="J112" s="4" t="n">
-        <v>349.09</v>
-      </c>
-      <c r="K112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">国家税务总局鹤壁市税务局稽查局依法查处鹤壁市国用商贸有限公司偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", </t>
-        </is>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
+      <c r="J112" s="4" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr"/>
+      <c r="L112" s="4" t="inlineStr"/>
+      <c r="M112" s="6" t="n">
+        <v>678.72</v>
+      </c>
+      <c r="N112" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243432/content.html</t>
         </is>
@@ -5863,7 +5981,7 @@
           <t>国家税务总局长治市税务局稽查局依法查处潞城市雨田实业有限责任公司第一加油站偷税案件</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -5889,15 +6007,13 @@
           <t>潞城市雨田实业有限责任公司</t>
         </is>
       </c>
-      <c r="J113" s="4" t="n">
-        <v>308.12</v>
-      </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局长治市税务局稽查局依法查处潞城市雨田实业有限责任公司第一加油站偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chin</t>
-        </is>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
+      <c r="J113" s="4" t="inlineStr"/>
+      <c r="K113" s="4" t="inlineStr"/>
+      <c r="L113" s="4" t="inlineStr"/>
+      <c r="M113" s="6" t="n">
+        <v>662.45</v>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243430/content.html</t>
         </is>
@@ -5917,7 +6033,7 @@
           <t>“个人账户”巧变“藏钱罐”“移花接木”终被查——揭开泰州市姜堰区胜利加油站隐匿收入偷税真相</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5941,7 +6057,9 @@
       </c>
       <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="4" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr"/>
+      <c r="N114" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243429/content.html</t>
         </is>
@@ -5961,7 +6079,7 @@
           <t>“消失”油款背后的“隐秘”操作——还原九江市浔西能源有限公司经开区加油站偷税真相</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -5985,7 +6103,9 @@
       </c>
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="4" t="inlineStr">
+      <c r="L115" s="4" t="inlineStr"/>
+      <c r="M115" s="4" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243427/content.html</t>
         </is>
@@ -6005,7 +6125,7 @@
           <t>油款收入“耍花招”背后的“神操作”——揭开湖南省陈攀好能源有限责任公司隐匿收入偷税面纱</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6033,7 +6153,9 @@
       </c>
       <c r="J116" s="4" t="inlineStr"/>
       <c r="K116" s="4" t="inlineStr"/>
-      <c r="L116" s="4" t="inlineStr">
+      <c r="L116" s="4" t="inlineStr"/>
+      <c r="M116" s="4" t="inlineStr"/>
+      <c r="N116" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243425/content.html</t>
         </is>
@@ -6053,7 +6175,7 @@
           <t>税务部门依法查处MCN机构、网络主播涉税违法案件 平台经营主体合规经营才能行稳致远</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -6072,12 +6194,10 @@
       <c r="H117" s="4" t="inlineStr"/>
       <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="4" t="inlineStr"/>
-      <c r="K117" s="4" t="inlineStr">
-        <is>
-          <t>税务部门依法查处MCN机构、网络主播涉税违法案件 平台经营主体合规经营才能行稳致远_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chin</t>
-        </is>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
+      <c r="K117" s="4" t="inlineStr"/>
+      <c r="L117" s="4" t="inlineStr"/>
+      <c r="M117" s="4" t="inlineStr"/>
+      <c r="N117" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243220/content.html</t>
         </is>
@@ -6097,7 +6217,7 @@
           <t>网络直播公司（MCN机构）的偷税“生意经”——揭秘河北楚鸣文化传媒有限公司涉税违法案件</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6125,7 +6245,9 @@
       </c>
       <c r="J118" s="4" t="inlineStr"/>
       <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="4" t="inlineStr">
+      <c r="L118" s="4" t="inlineStr"/>
+      <c r="M118" s="4" t="inlineStr"/>
+      <c r="N118" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243219/content.html</t>
         </is>
@@ -6145,7 +6267,7 @@
           <t>“头部”主播的“零报税”玄机——还原湖南颜客文化传媒有限公司涉税违法真相</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6173,7 +6295,9 @@
       </c>
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="4" t="inlineStr">
+      <c r="L119" s="4" t="inlineStr"/>
+      <c r="M119" s="4" t="inlineStr"/>
+      <c r="N119" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243217/content.html</t>
         </is>
@@ -6193,7 +6317,7 @@
           <t>粉丝超百万，纳税仅五万？——揭秘直播带货主播李呈祥隐匿收入偷税案件</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6217,7 +6341,9 @@
       <c r="I120" s="4" t="inlineStr"/>
       <c r="J120" s="4" t="inlineStr"/>
       <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr">
+      <c r="L120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr"/>
+      <c r="N120" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243215/content.html</t>
         </is>
@@ -6237,7 +6363,7 @@
           <t>国家税务总局沈阳市税务局第三稽查局依法查处网络主播李呈祥偷税案件</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -6259,15 +6385,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="4" t="n">
-        <v>243.5</v>
-      </c>
-      <c r="K121" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局沈阳市税务局第三稽查局依法查处网络主播李呈祥偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", we</t>
-        </is>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr"/>
+      <c r="L121" s="4" t="inlineStr"/>
+      <c r="M121" s="6" t="n">
+        <v>402.14</v>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5243214/content.html</t>
         </is>
@@ -6287,7 +6411,7 @@
           <t>注销登记心存侥幸企图逃税 隐匿出口应征税收入最终被查——揭秘上海悟瀚进出口有限公司偷逃税款案件</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6319,7 +6443,9 @@
       </c>
       <c r="J122" s="4" t="inlineStr"/>
       <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr">
+      <c r="L122" s="4" t="inlineStr"/>
+      <c r="M122" s="4" t="inlineStr"/>
+      <c r="N122" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242905/content.html</t>
         </is>
@@ -6339,7 +6465,7 @@
           <t>注销公司“掩盖”偷税终现形——还原莒南县宇飞食品有限公司偷税案真相</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D123" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6367,7 +6493,9 @@
       </c>
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr">
+      <c r="L123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="inlineStr"/>
+      <c r="N123" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242903/content.html</t>
         </is>
@@ -6405,15 +6533,11 @@
       </c>
       <c r="H124" s="4" t="inlineStr"/>
       <c r="I124" s="4" t="inlineStr"/>
-      <c r="J124" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="K124" s="4" t="inlineStr">
-        <is>
-          <t>团伙作案骗享优惠 借壳虚开30亿元——空壳农民专业合作社骗享涉农税收优惠政策虚开增值税普通发票被查处_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCod</t>
-        </is>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr"/>
+      <c r="L124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242494/content.html</t>
         </is>
@@ -6433,7 +6557,7 @@
           <t>虚假申报加计抵减钻空子 破产清算难掩偷税事实——揭露四川聚祥达物流有限公司骗享增值税加计抵减税费优惠偷税真相</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6461,7 +6585,9 @@
       </c>
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="4" t="inlineStr">
+      <c r="L125" s="4" t="inlineStr"/>
+      <c r="M125" s="4" t="inlineStr"/>
+      <c r="N125" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242492/content.html</t>
         </is>
@@ -6481,7 +6607,7 @@
           <t>账外藏金 拒交凭据 隐匿收入的“数据之谜”——揭秘河南千年冷链设备有限公司违规享受小微企业税费优惠偷税案</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6513,7 +6639,9 @@
       </c>
       <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr"/>
-      <c r="L126" s="4" t="inlineStr">
+      <c r="L126" s="4" t="inlineStr"/>
+      <c r="M126" s="4" t="inlineStr"/>
+      <c r="N126" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242490/content.html</t>
         </is>
@@ -6533,7 +6661,7 @@
           <t>国家税务总局黔东南州税务局稽查局依法查处凯里市个体工商户业主项祖顺拆分收入骗享小规模纳税人税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -6555,15 +6683,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="4" t="n">
-        <v>246.93</v>
-      </c>
-      <c r="K127" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局黔东南州税务局稽查局依法查处凯里市个体工商户业主项祖顺拆分收入骗享小规模纳税人税费优惠偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", website</t>
-        </is>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr"/>
+      <c r="L127" s="4" t="inlineStr"/>
+      <c r="M127" s="6" t="n">
+        <v>445.28</v>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242487/content.html</t>
         </is>
@@ -6583,7 +6709,7 @@
           <t>“白油”变“砂石”背后的玄机 ——揭秘涉税中介阳泉市易创商务服务有限公司及其实际控制人任宇宙虚开增值税专用发票案</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6607,7 +6733,9 @@
       <c r="I128" s="4" t="inlineStr"/>
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr"/>
-      <c r="L128" s="4" t="inlineStr">
+      <c r="L128" s="4" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr"/>
+      <c r="N128" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242101/content.html</t>
         </is>
@@ -6627,7 +6755,7 @@
           <t>山西省阳泉市税警联合依法查处涉税中介阳泉市易创商务服务有限公司及其实际控制人任宇宙虚开增值税专用发票案件</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -6658,12 +6786,12 @@
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr"/>
-      <c r="K129" s="4" t="inlineStr">
-        <is>
-          <t>山西省阳泉市税警联合依法查处涉税中介阳泉市易创商务服务有限公司及其实际控制人任宇宙虚开增值税专用发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteC</t>
-        </is>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
+      <c r="K129" s="4" t="inlineStr"/>
+      <c r="L129" s="4" t="inlineStr"/>
+      <c r="M129" s="6" t="n">
+        <v>21500</v>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242100/content.html</t>
         </is>
@@ -6683,7 +6811,7 @@
           <t>国家税务总局牡丹江市税务局依法查处一起代理办税人员与税务人员勾连勾兑虚开增值税专用发票案件</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -6702,12 +6830,12 @@
       <c r="H130" s="4" t="inlineStr"/>
       <c r="I130" s="4" t="inlineStr"/>
       <c r="J130" s="4" t="inlineStr"/>
-      <c r="K130" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局牡丹江市税务局依法查处一起代理办税人员与税务人员勾连勾兑虚开增值税专用发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "</t>
-        </is>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
+      <c r="K130" s="4" t="inlineStr"/>
+      <c r="L130" s="4" t="inlineStr"/>
+      <c r="M130" s="6" t="n">
+        <v>25300</v>
+      </c>
+      <c r="N130" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242093/content.html</t>
         </is>
@@ -6727,7 +6855,7 @@
           <t>内蒙古兴安盟税警联合依法查处涉税中介兴安盟中呈财务咨询有限公司及其法定代表人倪冬雪虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -6754,12 +6882,12 @@
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr"/>
-      <c r="K131" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古兴安盟税警联合依法查处涉税中介兴安盟中呈财务咨询有限公司及其法定代表人倪冬雪虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCod</t>
-        </is>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
+      <c r="K131" s="4" t="inlineStr"/>
+      <c r="L131" s="4" t="inlineStr"/>
+      <c r="M131" s="6" t="n">
+        <v>13300</v>
+      </c>
+      <c r="N131" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242098/content.html</t>
         </is>
@@ -6779,7 +6907,7 @@
           <t>“监守自盗”的不法中介——揭秘涉税中介安徽盛乾会计服务有限公司及其实际控制人胡洋虚开增值税专用发票案</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6807,7 +6935,9 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr">
+      <c r="L132" s="4" t="inlineStr"/>
+      <c r="M132" s="4" t="inlineStr"/>
+      <c r="N132" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242096/content.html</t>
         </is>
@@ -6827,7 +6957,7 @@
           <t>安徽省滁州市税警联合依法查处涉税中介安徽盛乾会计服务有限公司及其实际控制人胡洋虚开增值税专用发票案件</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -6858,12 +6988,12 @@
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr"/>
-      <c r="K133" s="4" t="inlineStr">
-        <is>
-          <t>安徽省滁州市税警联合依法查处涉税中介安徽盛乾会计服务有限公司及其实际控制人胡洋虚开增值税专用发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCod</t>
-        </is>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
+      <c r="K133" s="4" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr"/>
+      <c r="M133" s="6" t="n">
+        <v>398</v>
+      </c>
+      <c r="N133" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5242095/content.html</t>
         </is>
@@ -6883,7 +7013,7 @@
           <t>全员“兼职”的研发团队 ——揭秘陕西永明煤矿有限公司骗享研发费用加计扣除税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6915,7 +7045,9 @@
       </c>
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr">
+      <c r="L134" s="4" t="inlineStr"/>
+      <c r="M134" s="4" t="inlineStr"/>
+      <c r="N134" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5241692/content.html</t>
         </is>
@@ -6935,7 +7067,7 @@
           <t>客服跨界“变身”工程师 ——揭秘宁波红芮信息科技有限公司骗享研发费用加计扣除税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D135" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -6963,7 +7095,9 @@
       </c>
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="4" t="inlineStr">
+      <c r="L135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5241690/content.html</t>
         </is>
@@ -6983,7 +7117,7 @@
           <t>CSO公司“无中生有”的推广成本 ——揭秘龙岩亿懿生辉企业管理咨询服务有限公司骗享小微企业所得税优惠偷税案件</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7011,7 +7145,9 @@
       </c>
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="4" t="inlineStr">
+      <c r="L136" s="4" t="inlineStr"/>
+      <c r="M136" s="4" t="inlineStr"/>
+      <c r="N136" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5241686/content.html</t>
         </is>
@@ -7031,7 +7167,7 @@
           <t>借“马甲”搞假策划 虚构服务真偷税——揭秘四川仁远医疗科技有限公司骗享小微企业所得税优惠偷税案件</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7063,7 +7199,9 @@
       </c>
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr"/>
-      <c r="L137" s="4" t="inlineStr">
+      <c r="L137" s="4" t="inlineStr"/>
+      <c r="M137" s="4" t="inlineStr"/>
+      <c r="N137" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5241683/content.html</t>
         </is>
@@ -7083,7 +7221,7 @@
           <t>国家税务总局海南省税务局第一稽查局依法查处欧丽家公司隐匿未开票收入偷税案件</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7109,15 +7247,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr"/>
-      <c r="J138" s="4" t="n">
+      <c r="J138" s="4" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr"/>
+      <c r="L138" s="4" t="inlineStr"/>
+      <c r="M138" s="6" t="n">
         <v>1256.98</v>
       </c>
-      <c r="K138" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局海南省税务局第一稽查局依法查处欧丽家公司隐匿未开票收入偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax</t>
-        </is>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
+      <c r="N138" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5241011/content.html</t>
         </is>
@@ -7137,7 +7273,7 @@
           <t>千万利润却“账面亏损”个人账户成“秘密金库”——还原重庆多笠原食品有限公司隐匿未开票收入偷税真相</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7165,7 +7301,9 @@
       </c>
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="4" t="inlineStr">
+      <c r="L139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5241010/content.html</t>
         </is>
@@ -7185,7 +7323,7 @@
           <t>“明星”物业暗藏的税收算计——揭开怀化泰和物业服务有限公司隐匿未开票收入偷税真相</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7209,7 +7347,9 @@
       </c>
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr"/>
-      <c r="L140" s="4" t="inlineStr">
+      <c r="L140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr"/>
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5241008/content.html</t>
         </is>
@@ -7229,7 +7369,7 @@
           <t>“不知所踪”的黄金研发投入——深圳金斯达应用材料有限公司虚列研发费用偷税真相</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7249,7 +7389,9 @@
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="4" t="inlineStr">
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr"/>
+      <c r="N141" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5240517/content.html</t>
         </is>
@@ -7269,7 +7411,7 @@
           <t>国家税务总局深圳市税务局稽查局依法查处深圳金斯达应用材料有限公司骗享研发费用加计扣除税收优惠偷税案件</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7295,15 +7437,15 @@
           <t>深圳金斯达应用材料有限公司</t>
         </is>
       </c>
-      <c r="J142" s="4" t="n">
+      <c r="J142" s="6" t="n">
         <v>1621.16</v>
       </c>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局深圳市税务局稽查局依法查处深圳金斯达应用材料有限公司骗享研发费用加计扣除税收优惠偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCod</t>
-        </is>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
+      <c r="K142" s="4" t="inlineStr"/>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="6" t="n">
+        <v>3618.15</v>
+      </c>
+      <c r="N142" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5240516/content.html</t>
         </is>
@@ -7323,7 +7465,7 @@
           <t>国家税务总局嘉兴市税务局第一稽查局依法查处嘉善景盛混凝土制品有限公司骗享研发费用加计扣除</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7345,15 +7487,13 @@
           <t>嘉善景盛混凝土制品有限公司</t>
         </is>
       </c>
-      <c r="J143" s="4" t="n">
-        <v>307.91</v>
-      </c>
-      <c r="K143" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局嘉兴市税务局第一稽查局依法查处嘉善景盛混凝土制品有限公司骗享研发费用加计扣除_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "c</t>
-        </is>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
+      <c r="J143" s="4" t="inlineStr"/>
+      <c r="K143" s="4" t="inlineStr"/>
+      <c r="L143" s="4" t="inlineStr"/>
+      <c r="M143" s="6" t="n">
+        <v>609.14</v>
+      </c>
+      <c r="N143" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5240514/content.html</t>
         </is>
@@ -7373,7 +7513,7 @@
           <t>国家税务总局苏州工业园区税务局稽查局依法查处力软信息技术（苏州）有限公司骗享小微企业税收优惠偷税案件</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7399,15 +7539,15 @@
           <t>力软信息技术（苏州）有限公司</t>
         </is>
       </c>
-      <c r="J144" s="4" t="n">
+      <c r="J144" s="6" t="n">
         <v>78.27</v>
       </c>
-      <c r="K144" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局苏州工业园区税务局稽查局依法查处力软信息技术（苏州）有限公司骗享小微企业税收优惠偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCod</t>
-        </is>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
+      <c r="K144" s="4" t="inlineStr"/>
+      <c r="L144" s="4" t="inlineStr"/>
+      <c r="M144" s="6" t="n">
+        <v>177.57</v>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5240512/content.html</t>
         </is>
@@ -7427,7 +7567,7 @@
           <t>“奇怪”的85家废品回收站——揭秘东至县荣峰再生资源回收站暨盛荣峰偷税案</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
+      <c r="D145" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7451,7 +7591,9 @@
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="4" t="inlineStr">
+      <c r="L145" s="4" t="inlineStr"/>
+      <c r="M145" s="4" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5240044/content.html</t>
         </is>
@@ -7471,7 +7613,7 @@
           <t>运输公司百余笔业务的“拆分戏法”——揭秘阿拉尔市宏润运输有限公司拆分经营骗享税费优惠偷税案</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7499,7 +7641,9 @@
       </c>
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="4" t="inlineStr">
+      <c r="L146" s="4" t="inlineStr"/>
+      <c r="M146" s="4" t="inlineStr"/>
+      <c r="N146" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5240041/content.html</t>
         </is>
@@ -7519,7 +7663,7 @@
           <t>国家税务总局阿拉尔税务局稽查局依法查处宏润运输有限公司拆分经营骗享小规模纳税人税费优惠偷税案件</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7545,15 +7689,13 @@
           <t>宏润运输有限公司</t>
         </is>
       </c>
-      <c r="J147" s="4" t="n">
-        <v>61.97</v>
-      </c>
-      <c r="K147" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局阿拉尔税务局稽查局依法查处宏润运输有限公司拆分经营骗享小规模纳税人税费优惠偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode =</t>
-        </is>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
+      <c r="J147" s="4" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr"/>
+      <c r="L147" s="4" t="inlineStr"/>
+      <c r="M147" s="6" t="n">
+        <v>142.31</v>
+      </c>
+      <c r="N147" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5240036/content.html</t>
         </is>
@@ -7573,7 +7715,7 @@
           <t>悬殊的纳税申报背后隐藏的“玄机”——揭秘网络主播乐传曲偷税案</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D148" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7597,7 +7739,9 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr">
+      <c r="L148" s="4" t="inlineStr"/>
+      <c r="M148" s="4" t="inlineStr"/>
+      <c r="N148" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5239389/content.html</t>
         </is>
@@ -7617,7 +7761,7 @@
           <t>深圳市税务、海关、外汇等部门联合依法查处一起出口应征税货物未申报偷税案件</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7639,15 +7783,11 @@
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr"/>
-      <c r="J149" s="4" t="n">
-        <v>12900</v>
-      </c>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>深圳市税务、海关、外汇等部门联合依法查处一起出口应征税货物未申报偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax"</t>
-        </is>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
+      <c r="J149" s="4" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr"/>
+      <c r="L149" s="4" t="inlineStr"/>
+      <c r="M149" s="4" t="inlineStr"/>
+      <c r="N149" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5239385/content.html</t>
         </is>
@@ -7667,7 +7807,7 @@
           <t>千万厂房三折成交 吃亏是假逃税是真——揭秘宁波市奉化斯莫森服装辅料厂偷逃税案</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="D150" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7695,7 +7835,9 @@
       </c>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="4" t="inlineStr">
+      <c r="L150" s="4" t="inlineStr"/>
+      <c r="M150" s="4" t="inlineStr"/>
+      <c r="N150" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5239384/content.html</t>
         </is>
@@ -7715,7 +7857,7 @@
           <t>国家税务总局厦门市税务局第二稽查局依法查处厦门星曜贸易有限公司隐匿未开票收入偷税案件</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7741,15 +7883,13 @@
           <t>厦门星曜贸易有限公司</t>
         </is>
       </c>
-      <c r="J151" s="4" t="n">
+      <c r="J151" s="4" t="inlineStr"/>
+      <c r="K151" s="4" t="inlineStr"/>
+      <c r="L151" s="4" t="inlineStr"/>
+      <c r="M151" s="6" t="n">
         <v>156</v>
       </c>
-      <c r="K151" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局厦门市税务局第二稽查局依法查处厦门星曜贸易有限公司隐匿未开票收入偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chi</t>
-        </is>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
+      <c r="N151" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5239380/content.html</t>
         </is>
@@ -7769,7 +7909,7 @@
           <t>九家分公司“化整为零”骗享税收优惠政策——还原大理市寸四银庄商贸有限公司偷税真相</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="D152" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7793,7 +7933,9 @@
       </c>
       <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr"/>
-      <c r="L152" s="4" t="inlineStr">
+      <c r="L152" s="4" t="inlineStr"/>
+      <c r="M152" s="4" t="inlineStr"/>
+      <c r="N152" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5239379/content.html</t>
         </is>
@@ -7841,7 +7983,9 @@
       </c>
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr"/>
-      <c r="L153" s="4" t="inlineStr">
+      <c r="L153" s="4" t="inlineStr"/>
+      <c r="M153" s="4" t="inlineStr"/>
+      <c r="N153" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5238298/content.html</t>
         </is>
@@ -7861,7 +8005,7 @@
           <t>主板作弊“瞒天过海” 资金溯源“真相大白”——还原图木舒克市东城迎宾加油加气站利用作弊主板偷税真相</t>
         </is>
       </c>
-      <c r="D154" s="4" t="inlineStr">
+      <c r="D154" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -7885,7 +8029,9 @@
       </c>
       <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="4" t="inlineStr">
+      <c r="L154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr"/>
+      <c r="N154" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5238296/content.html</t>
         </is>
@@ -7905,7 +8051,7 @@
           <t>国家税务总局图木舒克税务局依法对东城迎宾加油加气站偷税案进行处理</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -7931,15 +8077,13 @@
           <t>东城迎宾加油加气站</t>
         </is>
       </c>
-      <c r="J155" s="4" t="n">
-        <v>533</v>
-      </c>
-      <c r="K155" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局图木舒克税务局依法对东城迎宾加油加气站偷税案进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", we</t>
-        </is>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
+      <c r="J155" s="4" t="inlineStr"/>
+      <c r="K155" s="4" t="inlineStr"/>
+      <c r="L155" s="4" t="inlineStr"/>
+      <c r="M155" s="6" t="n">
+        <v>793</v>
+      </c>
+      <c r="N155" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5238295/content.html</t>
         </is>
@@ -7983,7 +8127,9 @@
       <c r="I156" s="4" t="inlineStr"/>
       <c r="J156" s="4" t="inlineStr"/>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="4" t="inlineStr">
+      <c r="L156" s="4" t="inlineStr"/>
+      <c r="M156" s="4" t="inlineStr"/>
+      <c r="N156" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5238294/content.html</t>
         </is>
@@ -8003,7 +8149,7 @@
           <t>国家税务总局文山州税务局第二稽查局依法对丘北县树皮岔路加油站偷税案进行处理</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr">
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8029,15 +8175,13 @@
           <t>丘北县树皮岔路加油站</t>
         </is>
       </c>
-      <c r="J157" s="4" t="n">
-        <v>253</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局文山州税务局第二稽查局依法对丘北县树皮岔路加油站偷税案进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
+      <c r="J157" s="4" t="inlineStr"/>
+      <c r="K157" s="4" t="inlineStr"/>
+      <c r="L157" s="4" t="inlineStr"/>
+      <c r="M157" s="6" t="n">
+        <v>427</v>
+      </c>
+      <c r="N157" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5238293/content.html</t>
         </is>
@@ -8057,7 +8201,7 @@
           <t>山西省吕梁市税务局稽查局依法查处一起虚报研发费用加计扣除偷税案件</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8083,15 +8227,15 @@
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr"/>
-      <c r="J158" s="4" t="n">
+      <c r="J158" s="6" t="n">
         <v>796</v>
       </c>
-      <c r="K158" s="4" t="inlineStr">
-        <is>
-          <t>山西省吕梁市税务局稽查局依法查处一起虚报研发费用加计扣除偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", we</t>
-        </is>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
+      <c r="K158" s="4" t="inlineStr"/>
+      <c r="L158" s="4" t="inlineStr"/>
+      <c r="M158" s="6" t="n">
+        <v>1354</v>
+      </c>
+      <c r="N158" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5237739/content.html</t>
         </is>
@@ -8111,7 +8255,7 @@
           <t>深圳税警联合依法查处一起利用软件产品增值税“即征即退”税费优惠政策虚开发票案件</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8129,15 +8273,11 @@
       </c>
       <c r="H159" s="4" t="inlineStr"/>
       <c r="I159" s="4" t="inlineStr"/>
-      <c r="J159" s="4" t="n">
-        <v>8400</v>
-      </c>
-      <c r="K159" s="4" t="inlineStr">
-        <is>
-          <t>深圳税警联合依法查处一起利用软件产品增值税“即征即退”税费优惠政策虚开发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinat</t>
-        </is>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
+      <c r="J159" s="4" t="inlineStr"/>
+      <c r="K159" s="4" t="inlineStr"/>
+      <c r="L159" s="4" t="inlineStr"/>
+      <c r="M159" s="4" t="inlineStr"/>
+      <c r="N159" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5237735/content.html</t>
         </is>
@@ -8157,7 +8297,7 @@
           <t>国家税务总局上海市税务局第三稽查局依法对网络主播王子柏偷税案件进行处理</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8183,15 +8323,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr"/>
-      <c r="J160" s="4" t="n">
+      <c r="J160" s="4" t="inlineStr"/>
+      <c r="K160" s="4" t="inlineStr"/>
+      <c r="L160" s="4" t="inlineStr"/>
+      <c r="M160" s="6" t="n">
         <v>749</v>
       </c>
-      <c r="K160" s="4" t="inlineStr">
-        <is>
-          <t>国家税务总局上海市税务局第三稽查局依法对网络主播王子柏偷税案件进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax",</t>
-        </is>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
+      <c r="N160" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5237191/content.html</t>
         </is>
@@ -8211,7 +8349,7 @@
           <t>500万粉丝大V三年收入仅数万？ ——网络主播程虎虚假申报偷税真相揭露</t>
         </is>
       </c>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="D161" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -8231,7 +8369,9 @@
       <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="4" t="inlineStr">
+      <c r="L161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="inlineStr"/>
+      <c r="N161" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5237190/content.html</t>
         </is>
@@ -8251,7 +8391,7 @@
           <t>国家税务总局厦门市税务局第一稽查局依法对网络主播程虎偷税案件进行处理</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8273,15 +8413,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr"/>
-      <c r="J162" s="4" t="n">
+      <c r="J162" s="4" t="inlineStr"/>
+      <c r="K162" s="4" t="inlineStr"/>
+      <c r="L162" s="4" t="inlineStr"/>
+      <c r="M162" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="K162" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">国家税务总局厦门市税务局第一稽查局依法对网络主播程虎偷税案件进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", </t>
-        </is>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
+      <c r="N162" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5237189/content.html</t>
         </is>
@@ -8325,7 +8463,9 @@
       <c r="I163" s="4" t="inlineStr"/>
       <c r="J163" s="4" t="inlineStr"/>
       <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr">
+      <c r="L163" s="4" t="inlineStr"/>
+      <c r="M163" s="4" t="inlineStr"/>
+      <c r="N163" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5235878/content.html</t>
         </is>
@@ -8345,7 +8485,7 @@
           <t>四川省泸州市税务局稽查局依法对网络主播余洋偷税案件进行处理</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8371,15 +8511,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr"/>
-      <c r="J164" s="4" t="n">
+      <c r="J164" s="4" t="inlineStr"/>
+      <c r="K164" s="4" t="inlineStr"/>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="6" t="n">
         <v>805</v>
       </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>四川省泸州市税务局稽查局依法对网络主播余洋偷税案件进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", websi</t>
-        </is>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
+      <c r="N164" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5235877/content.html</t>
         </is>
@@ -8419,7 +8557,9 @@
       <c r="I165" s="4" t="inlineStr"/>
       <c r="J165" s="4" t="inlineStr"/>
       <c r="K165" s="4" t="inlineStr"/>
-      <c r="L165" s="4" t="inlineStr">
+      <c r="L165" s="4" t="inlineStr"/>
+      <c r="M165" s="4" t="inlineStr"/>
+      <c r="N165" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5235876/content.html</t>
         </is>
@@ -8439,7 +8579,7 @@
           <t>税务总局驻沈阳特派办组织辽宁省营口市税务局稽查局依法对网络主播田小龙偷税案件进行处理</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8465,15 +8605,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr"/>
-      <c r="J166" s="4" t="n">
+      <c r="J166" s="4" t="inlineStr"/>
+      <c r="K166" s="4" t="inlineStr"/>
+      <c r="L166" s="4" t="inlineStr"/>
+      <c r="M166" s="6" t="n">
         <v>735</v>
       </c>
-      <c r="K166" s="4" t="inlineStr">
-        <is>
-          <t>税务总局驻沈阳特派办组织辽宁省营口市税务局稽查局依法对网络主播田小龙偷税案件进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chi</t>
-        </is>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
+      <c r="N166" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5235875/content.html</t>
         </is>
@@ -8493,7 +8631,7 @@
           <t>收入性质“偷梁换柱” 异地申报“露出马脚”——网络主播金茜茜偷逃税款之真相大白</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="D167" s="7" t="inlineStr">
         <is>
           <t>深度揭秘</t>
         </is>
@@ -8517,7 +8655,9 @@
       <c r="I167" s="4" t="inlineStr"/>
       <c r="J167" s="4" t="inlineStr"/>
       <c r="K167" s="4" t="inlineStr"/>
-      <c r="L167" s="4" t="inlineStr">
+      <c r="L167" s="4" t="inlineStr"/>
+      <c r="M167" s="4" t="inlineStr"/>
+      <c r="N167" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5235874/content.html</t>
         </is>
@@ -8537,7 +8677,7 @@
           <t>湖南省常德市警税联合依法查处一起虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8559,15 +8699,13 @@
       </c>
       <c r="H168" s="4" t="inlineStr"/>
       <c r="I168" s="4" t="inlineStr"/>
-      <c r="J168" s="4" t="n">
-        <v>70000</v>
-      </c>
-      <c r="K168" s="4" t="inlineStr">
-        <is>
-          <t>湖南省常德市警税联合依法查处一起虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", websiteNa</t>
-        </is>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
+      <c r="J168" s="4" t="inlineStr"/>
+      <c r="K168" s="4" t="inlineStr"/>
+      <c r="L168" s="4" t="inlineStr"/>
+      <c r="M168" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="N168" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5235297/content.html</t>
         </is>
@@ -8587,7 +8725,7 @@
           <t>河南省税务部门依法查处一起加油站偷税案件</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8617,15 +8755,13 @@
           <t>一起加油站</t>
         </is>
       </c>
-      <c r="J169" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">河南省税务部门依法查处一起加油站偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", websiteName = </t>
-        </is>
-      </c>
-      <c r="L169" s="4" t="inlineStr">
+      <c r="J169" s="4" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr"/>
+      <c r="L169" s="4" t="inlineStr"/>
+      <c r="M169" s="6" t="n">
+        <v>328</v>
+      </c>
+      <c r="N169" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5235296/content.html</t>
         </is>
@@ -8645,7 +8781,7 @@
           <t>广东省惠州市警税联合依法查处一起利用小规模纳税人减免增值税政策虚开发票案件</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8667,15 +8803,11 @@
       </c>
       <c r="H170" s="4" t="inlineStr"/>
       <c r="I170" s="4" t="inlineStr"/>
-      <c r="J170" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K170" s="4" t="inlineStr">
-        <is>
-          <t>广东省惠州市警税联合依法查处一起利用小规模纳税人减免增值税政策虚开发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax</t>
-        </is>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
+      <c r="J170" s="4" t="inlineStr"/>
+      <c r="K170" s="4" t="inlineStr"/>
+      <c r="L170" s="4" t="inlineStr"/>
+      <c r="M170" s="4" t="inlineStr"/>
+      <c r="N170" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5232138/content.html</t>
         </is>
@@ -8695,7 +8827,7 @@
           <t>甘肃省天水市税务局稽查局依法对网络主播杨天奇偷税案件进行处理</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8721,15 +8853,15 @@
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr"/>
-      <c r="J171" s="4" t="n">
+      <c r="J171" s="6" t="n">
         <v>31.38</v>
       </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>甘肃省天水市税务局稽查局依法对网络主播杨天奇偷税案件进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", webs</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
+      <c r="K171" s="4" t="inlineStr"/>
+      <c r="L171" s="4" t="inlineStr"/>
+      <c r="M171" s="6" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="N171" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5223389/content.html</t>
         </is>
@@ -8749,7 +8881,7 @@
           <t>四川省攀枝花市警税联合依法查处一起向医药企业虚开增值税发票案件</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8771,15 +8903,11 @@
       </c>
       <c r="H172" s="4" t="inlineStr"/>
       <c r="I172" s="4" t="inlineStr"/>
-      <c r="J172" s="4" t="n">
-        <v>425</v>
-      </c>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>四川省攀枝花市警税联合依法查处一起向医药企业虚开增值税发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", web</t>
-        </is>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
+      <c r="J172" s="4" t="inlineStr"/>
+      <c r="K172" s="4" t="inlineStr"/>
+      <c r="L172" s="4" t="inlineStr"/>
+      <c r="M172" s="4" t="inlineStr"/>
+      <c r="N172" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5223386/content.html</t>
         </is>
@@ -8799,7 +8927,7 @@
           <t>河南省洛阳市税务局稽查局依法对网络主播马海涛、梁娜偷税案进行处理</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8825,15 +8953,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr"/>
-      <c r="J173" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="K173" s="4" t="inlineStr">
-        <is>
-          <t>河南省洛阳市税务局稽查局依法对网络主播马海涛、梁娜偷税案进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", we</t>
-        </is>
-      </c>
-      <c r="L173" s="4" t="inlineStr">
+      <c r="J173" s="4" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr"/>
+      <c r="L173" s="4" t="inlineStr"/>
+      <c r="M173" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="N173" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5221491/content.html</t>
         </is>
@@ -8853,7 +8979,7 @@
           <t>云南省文山壮族苗族自治州警税联合依法查处一起虚开农产品收购发票案件</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8875,15 +9001,13 @@
       </c>
       <c r="H174" s="4" t="inlineStr"/>
       <c r="I174" s="4" t="inlineStr"/>
-      <c r="J174" s="4" t="n">
+      <c r="J174" s="4" t="inlineStr"/>
+      <c r="K174" s="4" t="inlineStr"/>
+      <c r="L174" s="4" t="inlineStr"/>
+      <c r="M174" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="K174" s="4" t="inlineStr">
-        <is>
-          <t>云南省文山壮族苗族自治州警税联合依法查处一起虚开农产品收购发票案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", w</t>
-        </is>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
+      <c r="N174" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5221486/content.html</t>
         </is>
@@ -8903,7 +9027,7 @@
           <t>内蒙古自治区呼伦贝尔市税务局稽查局依法对网络主播周梦妮偷税案件进行处理</t>
         </is>
       </c>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8929,15 +9053,15 @@
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr"/>
-      <c r="J175" s="4" t="n">
+      <c r="J175" s="6" t="n">
         <v>10.26</v>
       </c>
-      <c r="K175" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古自治区呼伦贝尔市税务局稽查局依法对网络主播周梦妮偷税案件进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax",</t>
-        </is>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
+      <c r="K175" s="4" t="inlineStr"/>
+      <c r="L175" s="4" t="inlineStr"/>
+      <c r="M175" s="6" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="N175" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5220467/content.html</t>
         </is>
@@ -8957,7 +9081,7 @@
           <t>山东省税务局稽查局依法查处一起成品油生产企业偷税案件</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -8983,15 +9107,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr"/>
-      <c r="J176" s="4" t="n">
-        <v>15400</v>
-      </c>
-      <c r="K176" s="4" t="inlineStr">
-        <is>
-          <t>山东省税务局稽查局依法查处一起成品油生产企业偷税案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", websiteN</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
+      <c r="J176" s="4" t="inlineStr"/>
+      <c r="K176" s="4" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr"/>
+      <c r="M176" s="6" t="n">
+        <v>25200</v>
+      </c>
+      <c r="N176" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5220466/content.html</t>
         </is>
@@ -9011,7 +9133,7 @@
           <t>广西壮族自治区玉林市警税联合依法查处一起ETC通行费电子发票虚开案件</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9033,15 +9155,13 @@
       </c>
       <c r="H177" s="4" t="inlineStr"/>
       <c r="I177" s="4" t="inlineStr"/>
-      <c r="J177" s="4" t="n">
+      <c r="J177" s="4" t="inlineStr"/>
+      <c r="K177" s="4" t="inlineStr"/>
+      <c r="L177" s="4" t="inlineStr"/>
+      <c r="M177" s="6" t="n">
         <v>51600</v>
       </c>
-      <c r="K177" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">广西壮族自治区玉林市警税联合依法查处一起ETC通行费电子发票虚开案件_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", </t>
-        </is>
-      </c>
-      <c r="L177" s="4" t="inlineStr">
+      <c r="N177" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5220463/content.html</t>
         </is>
@@ -9061,7 +9181,7 @@
           <t>大连市税务局第一稽查局依法对网络主播王纯善偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9083,15 +9203,15 @@
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr"/>
-      <c r="J178" s="4" t="n">
+      <c r="J178" s="6" t="n">
         <v>218.3</v>
       </c>
-      <c r="K178" s="4" t="inlineStr">
-        <is>
-          <t>大连市税务局第一稽查局依法对网络主播王纯善偷逃税案件进行处理_国家税务总局 var websiteId = "a52dee227d764e87b641fe5b258cab14", websiteCode = "chinatax", webs</t>
-        </is>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
+      <c r="K178" s="4" t="inlineStr"/>
+      <c r="L178" s="4" t="inlineStr"/>
+      <c r="M178" s="6" t="n">
+        <v>653.61</v>
+      </c>
+      <c r="N178" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5216294/content.html</t>
         </is>
@@ -9111,7 +9231,7 @@
           <t>上海市警税联合依法查处一起利用多项税费优惠政策虚开发票案件</t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9135,7 +9255,9 @@
       <c r="I179" s="4" t="inlineStr"/>
       <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr"/>
-      <c r="L179" s="4" t="inlineStr">
+      <c r="L179" s="4" t="inlineStr"/>
+      <c r="M179" s="4" t="inlineStr"/>
+      <c r="N179" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5216293/content.html</t>
         </is>
@@ -9155,7 +9277,7 @@
           <t>云南省保山市税务局稽查局依法查处一起违规享受小规模纳税人减免增值税政策偷税案件</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9183,7 +9305,11 @@
       <c r="I180" s="4" t="inlineStr"/>
       <c r="J180" s="4" t="inlineStr"/>
       <c r="K180" s="4" t="inlineStr"/>
-      <c r="L180" s="4" t="inlineStr">
+      <c r="L180" s="4" t="inlineStr"/>
+      <c r="M180" s="6" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="N180" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5215729/content.html</t>
         </is>
@@ -9203,7 +9329,7 @@
           <t>青海省西宁经济技术开发区税务局稽查局依法查处一起骗取研发费用加计扣除政策案件</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9227,7 +9353,9 @@
       <c r="I181" s="4" t="inlineStr"/>
       <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr"/>
-      <c r="L181" s="4" t="inlineStr">
+      <c r="L181" s="4" t="inlineStr"/>
+      <c r="M181" s="4" t="inlineStr"/>
+      <c r="N181" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5215726/content.html</t>
         </is>
@@ -9271,7 +9399,9 @@
       <c r="I182" s="4" t="inlineStr"/>
       <c r="J182" s="4" t="inlineStr"/>
       <c r="K182" s="4" t="inlineStr"/>
-      <c r="L182" s="4" t="inlineStr">
+      <c r="L182" s="4" t="inlineStr"/>
+      <c r="M182" s="4" t="inlineStr"/>
+      <c r="N182" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5214154/content.html</t>
         </is>
@@ -9291,7 +9421,7 @@
           <t>厦门市税务局稽查局依法对影视制片人栾慧青偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9313,9 +9443,15 @@
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr"/>
-      <c r="J183" s="4" t="inlineStr"/>
+      <c r="J183" s="6" t="n">
+        <v>28.81</v>
+      </c>
       <c r="K183" s="4" t="inlineStr"/>
-      <c r="L183" s="4" t="inlineStr">
+      <c r="L183" s="4" t="inlineStr"/>
+      <c r="M183" s="6" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="N183" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5214114/content.html</t>
         </is>
@@ -9335,7 +9471,7 @@
           <t>湖北省武汉市税务局稽查局依法对财税中介人员李薇偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9361,9 +9497,15 @@
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="4" t="inlineStr"/>
+      <c r="J184" s="6" t="n">
+        <v>33.75</v>
+      </c>
       <c r="K184" s="4" t="inlineStr"/>
-      <c r="L184" s="4" t="inlineStr">
+      <c r="L184" s="4" t="inlineStr"/>
+      <c r="M184" s="6" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="N184" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5214116/content.html</t>
         </is>
@@ -9383,7 +9525,7 @@
           <t>天津市多部门联合依法查处一起骗取出口退税团伙案件</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9407,7 +9549,9 @@
       <c r="I185" s="4" t="inlineStr"/>
       <c r="J185" s="4" t="inlineStr"/>
       <c r="K185" s="4" t="inlineStr"/>
-      <c r="L185" s="4" t="inlineStr">
+      <c r="L185" s="4" t="inlineStr"/>
+      <c r="M185" s="4" t="inlineStr"/>
+      <c r="N185" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5214115/content.html</t>
         </is>
@@ -9427,7 +9571,7 @@
           <t>重庆市税务局第七稽查局依法对袁冰妍及其关联企业偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9455,7 +9599,11 @@
       <c r="I186" s="4" t="inlineStr"/>
       <c r="J186" s="4" t="inlineStr"/>
       <c r="K186" s="4" t="inlineStr"/>
-      <c r="L186" s="4" t="inlineStr">
+      <c r="L186" s="4" t="inlineStr"/>
+      <c r="M186" s="6" t="n">
+        <v>297.38</v>
+      </c>
+      <c r="N186" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5212208/content.html</t>
         </is>
@@ -9475,7 +9623,7 @@
           <t>广西壮族自治区税务局第三稽查局依法对网络主播吴川偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D187" s="4" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9501,9 +9649,15 @@
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr"/>
-      <c r="J187" s="4" t="inlineStr"/>
+      <c r="J187" s="6" t="n">
+        <v>827.91</v>
+      </c>
       <c r="K187" s="4" t="inlineStr"/>
-      <c r="L187" s="4" t="inlineStr">
+      <c r="L187" s="4" t="inlineStr"/>
+      <c r="M187" s="6" t="n">
+        <v>1359.08</v>
+      </c>
+      <c r="N187" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5212207/content.html</t>
         </is>
@@ -9523,7 +9677,7 @@
           <t>深圳市税务局稽查局依法查处一起未按规定履行代扣代缴税款义务案件</t>
         </is>
       </c>
-      <c r="D188" s="4" t="inlineStr">
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9542,8 +9696,12 @@
       <c r="H188" s="4" t="inlineStr"/>
       <c r="I188" s="4" t="inlineStr"/>
       <c r="J188" s="4" t="inlineStr"/>
-      <c r="K188" s="4" t="inlineStr"/>
-      <c r="L188" s="4" t="inlineStr">
+      <c r="K188" s="6" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="L188" s="4" t="inlineStr"/>
+      <c r="M188" s="4" t="inlineStr"/>
+      <c r="N188" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5212205/content.html</t>
         </is>
@@ -9563,7 +9721,7 @@
           <t>广东省汕头市警税联合依法查处一起利用增值税加计抵减政策虚开发票案件</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9587,7 +9745,9 @@
       <c r="I189" s="4" t="inlineStr"/>
       <c r="J189" s="4" t="inlineStr"/>
       <c r="K189" s="4" t="inlineStr"/>
-      <c r="L189" s="4" t="inlineStr">
+      <c r="L189" s="4" t="inlineStr"/>
+      <c r="M189" s="4" t="inlineStr"/>
+      <c r="N189" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5211460/content.html</t>
         </is>
@@ -9607,7 +9767,7 @@
           <t>河北省石家庄市警税联合依法查处一起利用小规模纳税人减免增值税政策虚开发票案件</t>
         </is>
       </c>
-      <c r="D190" s="4" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9631,7 +9791,9 @@
       <c r="I190" s="4" t="inlineStr"/>
       <c r="J190" s="4" t="inlineStr"/>
       <c r="K190" s="4" t="inlineStr"/>
-      <c r="L190" s="4" t="inlineStr">
+      <c r="L190" s="4" t="inlineStr"/>
+      <c r="M190" s="4" t="inlineStr"/>
+      <c r="N190" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5211024/content.html</t>
         </is>
@@ -9651,7 +9813,7 @@
           <t>四川省德阳市税务局稽查局依法查处一起接受虚开增值税专用发票并违规适用研发费用加计扣除案件</t>
         </is>
       </c>
-      <c r="D191" s="4" t="inlineStr">
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9675,7 +9837,9 @@
       <c r="I191" s="4" t="inlineStr"/>
       <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr"/>
-      <c r="L191" s="4" t="inlineStr">
+      <c r="L191" s="4" t="inlineStr"/>
+      <c r="M191" s="4" t="inlineStr"/>
+      <c r="N191" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5210225/content.html</t>
         </is>
@@ -9695,7 +9859,7 @@
           <t>上海市税务局第一稽查局依法查处一起机动车销售企业偷税案件</t>
         </is>
       </c>
-      <c r="D192" s="4" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9723,7 +9887,11 @@
       <c r="I192" s="4" t="inlineStr"/>
       <c r="J192" s="4" t="inlineStr"/>
       <c r="K192" s="4" t="inlineStr"/>
-      <c r="L192" s="4" t="inlineStr">
+      <c r="L192" s="4" t="inlineStr"/>
+      <c r="M192" s="6" t="n">
+        <v>10600</v>
+      </c>
+      <c r="N192" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5210226/content.html</t>
         </is>
@@ -9743,7 +9911,7 @@
           <t>福建省龙岩市税务局第二稽查局联合法院强制执行一起未依法办理个人所得税综合所得汇算清缴补税案件</t>
         </is>
       </c>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="D193" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9767,7 +9935,11 @@
       <c r="I193" s="4" t="inlineStr"/>
       <c r="J193" s="4" t="inlineStr"/>
       <c r="K193" s="4" t="inlineStr"/>
-      <c r="L193" s="4" t="inlineStr">
+      <c r="L193" s="4" t="inlineStr"/>
+      <c r="M193" s="6" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="N193" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5209750/content.html</t>
         </is>
@@ -9787,7 +9959,7 @@
           <t>安徽省宿州市税务局稽查局依法对网络主播吴思豪少缴税款案进行处理</t>
         </is>
       </c>
-      <c r="D194" s="4" t="inlineStr">
+      <c r="D194" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9813,9 +9985,15 @@
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr"/>
-      <c r="J194" s="4" t="inlineStr"/>
+      <c r="J194" s="6" t="n">
+        <v>210.57</v>
+      </c>
       <c r="K194" s="4" t="inlineStr"/>
-      <c r="L194" s="4" t="inlineStr">
+      <c r="L194" s="4" t="inlineStr"/>
+      <c r="M194" s="6" t="n">
+        <v>476.75</v>
+      </c>
+      <c r="N194" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5209748/content.html</t>
         </is>
@@ -9835,7 +10013,7 @@
           <t>上海市警税联合依法查处一起利用增值税加计抵减政策虚开发票骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D195" s="4" t="inlineStr">
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9859,7 +10037,9 @@
       <c r="I195" s="4" t="inlineStr"/>
       <c r="J195" s="4" t="inlineStr"/>
       <c r="K195" s="4" t="inlineStr"/>
-      <c r="L195" s="4" t="inlineStr">
+      <c r="L195" s="4" t="inlineStr"/>
+      <c r="M195" s="4" t="inlineStr"/>
+      <c r="N195" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5206704/content.html</t>
         </is>
@@ -9879,7 +10059,7 @@
           <t>贵州省税务等多部门联合依法查处一起骗取出口退税案件</t>
         </is>
       </c>
-      <c r="D196" s="4" t="inlineStr">
+      <c r="D196" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9903,7 +10083,11 @@
       <c r="I196" s="4" t="inlineStr"/>
       <c r="J196" s="4" t="inlineStr"/>
       <c r="K196" s="4" t="inlineStr"/>
-      <c r="L196" s="4" t="inlineStr">
+      <c r="L196" s="4" t="inlineStr"/>
+      <c r="M196" s="6" t="n">
+        <v>640</v>
+      </c>
+      <c r="N196" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5206703/content.html</t>
         </is>
@@ -9923,7 +10107,7 @@
           <t>江西省吉安市税务局稽查局依法查处一起虚开增值税普通发票案件</t>
         </is>
       </c>
-      <c r="D197" s="4" t="inlineStr">
+      <c r="D197" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9947,7 +10131,9 @@
       <c r="I197" s="4" t="inlineStr"/>
       <c r="J197" s="4" t="inlineStr"/>
       <c r="K197" s="4" t="inlineStr"/>
-      <c r="L197" s="4" t="inlineStr">
+      <c r="L197" s="4" t="inlineStr"/>
+      <c r="M197" s="4" t="inlineStr"/>
+      <c r="N197" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5205586/content.html</t>
         </is>
@@ -9967,7 +10153,7 @@
           <t>浙江省多部门联合依法查处一起骗取出口退税团伙案件</t>
         </is>
       </c>
-      <c r="D198" s="4" t="inlineStr">
+      <c r="D198" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -9991,7 +10177,11 @@
       <c r="I198" s="4" t="inlineStr"/>
       <c r="J198" s="4" t="inlineStr"/>
       <c r="K198" s="4" t="inlineStr"/>
-      <c r="L198" s="4" t="inlineStr">
+      <c r="L198" s="4" t="inlineStr"/>
+      <c r="M198" s="6" t="n">
+        <v>2913</v>
+      </c>
+      <c r="N198" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5201940/content.html</t>
         </is>
@@ -10011,7 +10201,7 @@
           <t>福建省税务部门依法查处一起虚开发票团伙骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10035,7 +10225,9 @@
       <c r="I199" s="4" t="inlineStr"/>
       <c r="J199" s="4" t="inlineStr"/>
       <c r="K199" s="4" t="inlineStr"/>
-      <c r="L199" s="4" t="inlineStr">
+      <c r="L199" s="4" t="inlineStr"/>
+      <c r="M199" s="4" t="inlineStr"/>
+      <c r="N199" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5201939/content.html</t>
         </is>
@@ -10055,7 +10247,7 @@
           <t>厦门市税务局稽查局依法对网络主播姚振宇偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D200" s="4" t="inlineStr">
+      <c r="D200" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10077,9 +10269,15 @@
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr"/>
-      <c r="J200" s="4" t="inlineStr"/>
+      <c r="J200" s="6" t="n">
+        <v>236.3</v>
+      </c>
       <c r="K200" s="4" t="inlineStr"/>
-      <c r="L200" s="4" t="inlineStr">
+      <c r="L200" s="4" t="inlineStr"/>
+      <c r="M200" s="6" t="n">
+        <v>545.8</v>
+      </c>
+      <c r="N200" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5192927/content.html</t>
         </is>
@@ -10099,7 +10297,7 @@
           <t>广西壮族自治区百色市警税联合依法查处一起虚开增值税专用发票骗取出口退税团伙案件</t>
         </is>
       </c>
-      <c r="D201" s="4" t="inlineStr">
+      <c r="D201" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10123,7 +10321,9 @@
       <c r="I201" s="4" t="inlineStr"/>
       <c r="J201" s="4" t="inlineStr"/>
       <c r="K201" s="4" t="inlineStr"/>
-      <c r="L201" s="4" t="inlineStr">
+      <c r="L201" s="4" t="inlineStr"/>
+      <c r="M201" s="4" t="inlineStr"/>
+      <c r="N201" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5192926/content.html</t>
         </is>
@@ -10143,7 +10343,7 @@
           <t>上海市税务局第四稽查局依法查处一起骗取留抵退税和偷税案件</t>
         </is>
       </c>
-      <c r="D202" s="4" t="inlineStr">
+      <c r="D202" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10171,7 +10371,9 @@
       <c r="I202" s="4" t="inlineStr"/>
       <c r="J202" s="4" t="inlineStr"/>
       <c r="K202" s="4" t="inlineStr"/>
-      <c r="L202" s="4" t="inlineStr">
+      <c r="L202" s="4" t="inlineStr"/>
+      <c r="M202" s="4" t="inlineStr"/>
+      <c r="N202" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5186220/content.html</t>
         </is>
@@ -10191,7 +10393,7 @@
           <t>辽宁省抚顺市税警联合依法查处一起涉税中介机构涉嫌组织虚开发票帮助他人偷逃税款案件</t>
         </is>
       </c>
-      <c r="D203" s="4" t="inlineStr">
+      <c r="D203" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10217,9 +10419,15 @@
         </is>
       </c>
       <c r="I203" s="4" t="inlineStr"/>
-      <c r="J203" s="4" t="inlineStr"/>
+      <c r="J203" s="6" t="n">
+        <v>5379</v>
+      </c>
       <c r="K203" s="4" t="inlineStr"/>
-      <c r="L203" s="4" t="inlineStr">
+      <c r="L203" s="4" t="inlineStr"/>
+      <c r="M203" s="6" t="n">
+        <v>5379</v>
+      </c>
+      <c r="N203" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5186219/content.html</t>
         </is>
@@ -10239,7 +10447,7 @@
           <t>山东省淄博市警税联合依法查处一起代开发票虚开案件</t>
         </is>
       </c>
-      <c r="D204" s="4" t="inlineStr">
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10263,7 +10471,9 @@
       <c r="I204" s="4" t="inlineStr"/>
       <c r="J204" s="4" t="inlineStr"/>
       <c r="K204" s="4" t="inlineStr"/>
-      <c r="L204" s="4" t="inlineStr">
+      <c r="L204" s="4" t="inlineStr"/>
+      <c r="M204" s="4" t="inlineStr"/>
+      <c r="N204" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5186217/content.html</t>
         </is>
@@ -10283,7 +10493,7 @@
           <t>湖北省警税联合依法查处一起虚开增值税专用发票案件</t>
         </is>
       </c>
-      <c r="D205" s="4" t="inlineStr">
+      <c r="D205" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10307,7 +10517,11 @@
       <c r="I205" s="4" t="inlineStr"/>
       <c r="J205" s="4" t="inlineStr"/>
       <c r="K205" s="4" t="inlineStr"/>
-      <c r="L205" s="4" t="inlineStr">
+      <c r="L205" s="4" t="inlineStr"/>
+      <c r="M205" s="6" t="n">
+        <v>152</v>
+      </c>
+      <c r="N205" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5185689/content.html</t>
         </is>
@@ -10327,7 +10541,7 @@
           <t>西安市税务局第三稽查局依法对网络主播贾亚亚、加婵婵偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D206" s="4" t="inlineStr">
+      <c r="D206" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10349,9 +10563,15 @@
         </is>
       </c>
       <c r="I206" s="4" t="inlineStr"/>
-      <c r="J206" s="4" t="inlineStr"/>
+      <c r="J206" s="6" t="n">
+        <v>9.81</v>
+      </c>
       <c r="K206" s="4" t="inlineStr"/>
-      <c r="L206" s="4" t="inlineStr">
+      <c r="L206" s="4" t="inlineStr"/>
+      <c r="M206" s="6" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="N206" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5185199/content.html</t>
         </is>
@@ -10371,7 +10591,7 @@
           <t>河南省鹤壁市税务部门对一起涉税中介机构违规发布涉税虚假宣传信息进行处理</t>
         </is>
       </c>
-      <c r="D207" s="4" t="inlineStr">
+      <c r="D207" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10395,7 +10615,9 @@
       <c r="I207" s="4" t="inlineStr"/>
       <c r="J207" s="4" t="inlineStr"/>
       <c r="K207" s="4" t="inlineStr"/>
-      <c r="L207" s="4" t="inlineStr">
+      <c r="L207" s="4" t="inlineStr"/>
+      <c r="M207" s="4" t="inlineStr"/>
+      <c r="N207" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5185197/content.html</t>
         </is>
@@ -10415,7 +10637,7 @@
           <t>青岛市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D208" s="4" t="inlineStr">
+      <c r="D208" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10435,7 +10657,9 @@
       <c r="I208" s="4" t="inlineStr"/>
       <c r="J208" s="4" t="inlineStr"/>
       <c r="K208" s="4" t="inlineStr"/>
-      <c r="L208" s="4" t="inlineStr">
+      <c r="L208" s="4" t="inlineStr"/>
+      <c r="M208" s="4" t="inlineStr"/>
+      <c r="N208" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5183873/content.html</t>
         </is>
@@ -10455,7 +10679,7 @@
           <t>广西壮族自治区钦州市税务局稽查局依法查处一起物流企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D209" s="4" t="inlineStr">
+      <c r="D209" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10479,7 +10703,9 @@
       <c r="I209" s="4" t="inlineStr"/>
       <c r="J209" s="4" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr"/>
-      <c r="L209" s="4" t="inlineStr">
+      <c r="L209" s="4" t="inlineStr"/>
+      <c r="M209" s="4" t="inlineStr"/>
+      <c r="N209" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5183560/content.html</t>
         </is>
@@ -10499,7 +10725,7 @@
           <t>辽宁省阜新市税务局第一稽查局依法查处一起运输企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D210" s="4" t="inlineStr">
+      <c r="D210" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10523,7 +10749,9 @@
       <c r="I210" s="4" t="inlineStr"/>
       <c r="J210" s="4" t="inlineStr"/>
       <c r="K210" s="4" t="inlineStr"/>
-      <c r="L210" s="4" t="inlineStr">
+      <c r="L210" s="4" t="inlineStr"/>
+      <c r="M210" s="4" t="inlineStr"/>
+      <c r="N210" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5182847/content.html</t>
         </is>
@@ -10543,7 +10771,7 @@
           <t>黑龙江省鹤岗市税务局第一稽查局依法查处一起批发企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D211" s="4" t="inlineStr">
+      <c r="D211" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10567,7 +10795,9 @@
       <c r="I211" s="4" t="inlineStr"/>
       <c r="J211" s="4" t="inlineStr"/>
       <c r="K211" s="4" t="inlineStr"/>
-      <c r="L211" s="4" t="inlineStr">
+      <c r="L211" s="4" t="inlineStr"/>
+      <c r="M211" s="4" t="inlineStr"/>
+      <c r="N211" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5182846/content.html</t>
         </is>
@@ -10587,7 +10817,7 @@
           <t>大连市甘井子区税务部门对一起涉税中介机构违规发布涉税虚假宣传信息进行处理</t>
         </is>
       </c>
-      <c r="D212" s="4" t="inlineStr">
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10607,7 +10837,9 @@
       <c r="I212" s="4" t="inlineStr"/>
       <c r="J212" s="4" t="inlineStr"/>
       <c r="K212" s="4" t="inlineStr"/>
-      <c r="L212" s="4" t="inlineStr">
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="inlineStr"/>
+      <c r="N212" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5181654/content.html</t>
         </is>
@@ -10627,7 +10859,7 @@
           <t>海南省税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr">
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10651,7 +10883,9 @@
       <c r="I213" s="4" t="inlineStr"/>
       <c r="J213" s="4" t="inlineStr"/>
       <c r="K213" s="4" t="inlineStr"/>
-      <c r="L213" s="4" t="inlineStr">
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5181223/content.html</t>
         </is>
@@ -10671,7 +10905,7 @@
           <t>上海市税务局第五稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D214" s="4" t="inlineStr">
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10695,7 +10929,9 @@
       <c r="I214" s="4" t="inlineStr"/>
       <c r="J214" s="4" t="inlineStr"/>
       <c r="K214" s="4" t="inlineStr"/>
-      <c r="L214" s="4" t="inlineStr">
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="inlineStr"/>
+      <c r="N214" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5181006/content.html</t>
         </is>
@@ -10715,7 +10951,7 @@
           <t>浙江省温州市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D215" s="4" t="inlineStr">
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10739,7 +10975,9 @@
       <c r="I215" s="4" t="inlineStr"/>
       <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr"/>
-      <c r="L215" s="4" t="inlineStr">
+      <c r="L215" s="4" t="inlineStr"/>
+      <c r="M215" s="4" t="inlineStr"/>
+      <c r="N215" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5179304/content.html</t>
         </is>
@@ -10759,7 +10997,7 @@
           <t>陕西省榆林市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D216" s="4" t="inlineStr">
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10783,7 +11021,9 @@
       <c r="I216" s="4" t="inlineStr"/>
       <c r="J216" s="4" t="inlineStr"/>
       <c r="K216" s="4" t="inlineStr"/>
-      <c r="L216" s="4" t="inlineStr">
+      <c r="L216" s="4" t="inlineStr"/>
+      <c r="M216" s="4" t="inlineStr"/>
+      <c r="N216" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5179027/content.html</t>
         </is>
@@ -10803,7 +11043,7 @@
           <t>北京市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D217" s="4" t="inlineStr">
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10827,7 +11067,9 @@
       <c r="I217" s="4" t="inlineStr"/>
       <c r="J217" s="4" t="inlineStr"/>
       <c r="K217" s="4" t="inlineStr"/>
-      <c r="L217" s="4" t="inlineStr">
+      <c r="L217" s="4" t="inlineStr"/>
+      <c r="M217" s="4" t="inlineStr"/>
+      <c r="N217" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178723/content.html</t>
         </is>
@@ -10847,7 +11089,7 @@
           <t>福建省税务部门依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D218" s="4" t="inlineStr">
+      <c r="D218" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10871,7 +11113,9 @@
       <c r="I218" s="4" t="inlineStr"/>
       <c r="J218" s="4" t="inlineStr"/>
       <c r="K218" s="4" t="inlineStr"/>
-      <c r="L218" s="4" t="inlineStr">
+      <c r="L218" s="4" t="inlineStr"/>
+      <c r="M218" s="4" t="inlineStr"/>
+      <c r="N218" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178720/content.html</t>
         </is>
@@ -10891,7 +11135,7 @@
           <t>深圳市税务局第四稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D219" s="4" t="inlineStr">
+      <c r="D219" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10911,7 +11155,9 @@
       <c r="I219" s="4" t="inlineStr"/>
       <c r="J219" s="4" t="inlineStr"/>
       <c r="K219" s="4" t="inlineStr"/>
-      <c r="L219" s="4" t="inlineStr">
+      <c r="L219" s="4" t="inlineStr"/>
+      <c r="M219" s="4" t="inlineStr"/>
+      <c r="N219" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178662/content.html</t>
         </is>
@@ -10931,7 +11177,7 @@
           <t>海南省税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D220" s="4" t="inlineStr">
+      <c r="D220" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10955,7 +11201,9 @@
       <c r="I220" s="4" t="inlineStr"/>
       <c r="J220" s="4" t="inlineStr"/>
       <c r="K220" s="4" t="inlineStr"/>
-      <c r="L220" s="4" t="inlineStr">
+      <c r="L220" s="4" t="inlineStr"/>
+      <c r="M220" s="4" t="inlineStr"/>
+      <c r="N220" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178648/content.html</t>
         </is>
@@ -10975,7 +11223,7 @@
           <t>江苏省张家港保税区税务部门依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D221" s="4" t="inlineStr">
+      <c r="D221" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -10999,7 +11247,9 @@
       <c r="I221" s="4" t="inlineStr"/>
       <c r="J221" s="4" t="inlineStr"/>
       <c r="K221" s="4" t="inlineStr"/>
-      <c r="L221" s="4" t="inlineStr">
+      <c r="L221" s="4" t="inlineStr"/>
+      <c r="M221" s="4" t="inlineStr"/>
+      <c r="N221" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178647/content.html</t>
         </is>
@@ -11043,7 +11293,9 @@
       <c r="I222" s="4" t="inlineStr"/>
       <c r="J222" s="4" t="inlineStr"/>
       <c r="K222" s="4" t="inlineStr"/>
-      <c r="L222" s="4" t="inlineStr">
+      <c r="L222" s="4" t="inlineStr"/>
+      <c r="M222" s="4" t="inlineStr"/>
+      <c r="N222" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178620/content.html</t>
         </is>
@@ -11063,7 +11315,7 @@
           <t>重庆市税务局第六稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D223" s="4" t="inlineStr">
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11087,7 +11339,9 @@
       <c r="I223" s="4" t="inlineStr"/>
       <c r="J223" s="4" t="inlineStr"/>
       <c r="K223" s="4" t="inlineStr"/>
-      <c r="L223" s="4" t="inlineStr">
+      <c r="L223" s="4" t="inlineStr"/>
+      <c r="M223" s="4" t="inlineStr"/>
+      <c r="N223" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178612/content.html</t>
         </is>
@@ -11107,7 +11361,7 @@
           <t>河北省张家口市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D224" s="4" t="inlineStr">
+      <c r="D224" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11131,7 +11385,9 @@
       <c r="I224" s="4" t="inlineStr"/>
       <c r="J224" s="4" t="inlineStr"/>
       <c r="K224" s="4" t="inlineStr"/>
-      <c r="L224" s="4" t="inlineStr">
+      <c r="L224" s="4" t="inlineStr"/>
+      <c r="M224" s="4" t="inlineStr"/>
+      <c r="N224" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178598/content.html</t>
         </is>
@@ -11151,7 +11407,7 @@
           <t>安徽省淮北市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D225" s="4" t="inlineStr">
+      <c r="D225" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11175,7 +11431,9 @@
       <c r="I225" s="4" t="inlineStr"/>
       <c r="J225" s="4" t="inlineStr"/>
       <c r="K225" s="4" t="inlineStr"/>
-      <c r="L225" s="4" t="inlineStr">
+      <c r="L225" s="4" t="inlineStr"/>
+      <c r="M225" s="4" t="inlineStr"/>
+      <c r="N225" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178596/content.html</t>
         </is>
@@ -11195,7 +11453,7 @@
           <t>云南省西双版纳州税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D226" s="4" t="inlineStr">
+      <c r="D226" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11219,7 +11477,9 @@
       <c r="I226" s="4" t="inlineStr"/>
       <c r="J226" s="4" t="inlineStr"/>
       <c r="K226" s="4" t="inlineStr"/>
-      <c r="L226" s="4" t="inlineStr">
+      <c r="L226" s="4" t="inlineStr"/>
+      <c r="M226" s="4" t="inlineStr"/>
+      <c r="N226" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178588/content.html</t>
         </is>
@@ -11239,7 +11499,7 @@
           <t>辽宁省鞍山市税务局稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D227" s="4" t="inlineStr">
+      <c r="D227" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11263,7 +11523,9 @@
       <c r="I227" s="4" t="inlineStr"/>
       <c r="J227" s="4" t="inlineStr"/>
       <c r="K227" s="4" t="inlineStr"/>
-      <c r="L227" s="4" t="inlineStr">
+      <c r="L227" s="4" t="inlineStr"/>
+      <c r="M227" s="4" t="inlineStr"/>
+      <c r="N227" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178566/content.html</t>
         </is>
@@ -11283,7 +11545,7 @@
           <t>海南省税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D228" s="4" t="inlineStr">
+      <c r="D228" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11307,7 +11569,9 @@
       <c r="I228" s="4" t="inlineStr"/>
       <c r="J228" s="4" t="inlineStr"/>
       <c r="K228" s="4" t="inlineStr"/>
-      <c r="L228" s="4" t="inlineStr">
+      <c r="L228" s="4" t="inlineStr"/>
+      <c r="M228" s="4" t="inlineStr"/>
+      <c r="N228" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178552/content.html</t>
         </is>
@@ -11327,7 +11591,7 @@
           <t>深圳市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D229" s="4" t="inlineStr">
+      <c r="D229" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11347,7 +11611,9 @@
       <c r="I229" s="4" t="inlineStr"/>
       <c r="J229" s="4" t="inlineStr"/>
       <c r="K229" s="4" t="inlineStr"/>
-      <c r="L229" s="4" t="inlineStr">
+      <c r="L229" s="4" t="inlineStr"/>
+      <c r="M229" s="4" t="inlineStr"/>
+      <c r="N229" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178520/content.html</t>
         </is>
@@ -11367,7 +11633,7 @@
           <t>甘肃省天水市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="D230" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11391,7 +11657,9 @@
       <c r="I230" s="4" t="inlineStr"/>
       <c r="J230" s="4" t="inlineStr"/>
       <c r="K230" s="4" t="inlineStr"/>
-      <c r="L230" s="4" t="inlineStr">
+      <c r="L230" s="4" t="inlineStr"/>
+      <c r="M230" s="4" t="inlineStr"/>
+      <c r="N230" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178477/content.html</t>
         </is>
@@ -11411,7 +11679,7 @@
           <t>辽宁省辽阳市税务部门依法查处一起骗取留抵退税案</t>
         </is>
       </c>
-      <c r="D231" s="4" t="inlineStr">
+      <c r="D231" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11435,7 +11703,9 @@
       <c r="I231" s="4" t="inlineStr"/>
       <c r="J231" s="4" t="inlineStr"/>
       <c r="K231" s="4" t="inlineStr"/>
-      <c r="L231" s="4" t="inlineStr">
+      <c r="L231" s="4" t="inlineStr"/>
+      <c r="M231" s="4" t="inlineStr"/>
+      <c r="N231" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178448/content.html</t>
         </is>
@@ -11455,7 +11725,7 @@
           <t>北京市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="D232" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11479,7 +11749,9 @@
       <c r="I232" s="4" t="inlineStr"/>
       <c r="J232" s="4" t="inlineStr"/>
       <c r="K232" s="4" t="inlineStr"/>
-      <c r="L232" s="4" t="inlineStr">
+      <c r="L232" s="4" t="inlineStr"/>
+      <c r="M232" s="4" t="inlineStr"/>
+      <c r="N232" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178403/content.html</t>
         </is>
@@ -11499,7 +11771,7 @@
           <t>宁夏回族自治区固原市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="D233" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11523,7 +11795,9 @@
       <c r="I233" s="4" t="inlineStr"/>
       <c r="J233" s="4" t="inlineStr"/>
       <c r="K233" s="4" t="inlineStr"/>
-      <c r="L233" s="4" t="inlineStr">
+      <c r="L233" s="4" t="inlineStr"/>
+      <c r="M233" s="4" t="inlineStr"/>
+      <c r="N233" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178396/content.html</t>
         </is>
@@ -11543,7 +11817,7 @@
           <t>湖南省衡阳市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D234" s="4" t="inlineStr">
+      <c r="D234" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11567,7 +11841,9 @@
       <c r="I234" s="4" t="inlineStr"/>
       <c r="J234" s="4" t="inlineStr"/>
       <c r="K234" s="4" t="inlineStr"/>
-      <c r="L234" s="4" t="inlineStr">
+      <c r="L234" s="4" t="inlineStr"/>
+      <c r="M234" s="4" t="inlineStr"/>
+      <c r="N234" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178357/content.html</t>
         </is>
@@ -11587,7 +11863,7 @@
           <t>陕西省西安市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D235" s="4" t="inlineStr">
+      <c r="D235" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11611,7 +11887,9 @@
       <c r="I235" s="4" t="inlineStr"/>
       <c r="J235" s="4" t="inlineStr"/>
       <c r="K235" s="4" t="inlineStr"/>
-      <c r="L235" s="4" t="inlineStr">
+      <c r="L235" s="4" t="inlineStr"/>
+      <c r="M235" s="4" t="inlineStr"/>
+      <c r="N235" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178340/content.html</t>
         </is>
@@ -11631,7 +11909,7 @@
           <t>辽宁省丹东市税务局稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D236" s="4" t="inlineStr">
+      <c r="D236" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11655,7 +11933,9 @@
       <c r="I236" s="4" t="inlineStr"/>
       <c r="J236" s="4" t="inlineStr"/>
       <c r="K236" s="4" t="inlineStr"/>
-      <c r="L236" s="4" t="inlineStr">
+      <c r="L236" s="4" t="inlineStr"/>
+      <c r="M236" s="4" t="inlineStr"/>
+      <c r="N236" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178320/content.html</t>
         </is>
@@ -11675,7 +11955,7 @@
           <t>江苏省南京市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D237" s="4" t="inlineStr">
+      <c r="D237" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11699,7 +11979,9 @@
       <c r="I237" s="4" t="inlineStr"/>
       <c r="J237" s="4" t="inlineStr"/>
       <c r="K237" s="4" t="inlineStr"/>
-      <c r="L237" s="4" t="inlineStr">
+      <c r="L237" s="4" t="inlineStr"/>
+      <c r="M237" s="4" t="inlineStr"/>
+      <c r="N237" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178298/content.html</t>
         </is>
@@ -11719,7 +12001,7 @@
           <t>广西壮族自治区税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D238" s="4" t="inlineStr">
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11743,7 +12025,9 @@
       <c r="I238" s="4" t="inlineStr"/>
       <c r="J238" s="4" t="inlineStr"/>
       <c r="K238" s="4" t="inlineStr"/>
-      <c r="L238" s="4" t="inlineStr">
+      <c r="L238" s="4" t="inlineStr"/>
+      <c r="M238" s="4" t="inlineStr"/>
+      <c r="N238" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178266/content.html</t>
         </is>
@@ -11763,7 +12047,7 @@
           <t>河北省秦皇岛市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D239" s="4" t="inlineStr">
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11787,7 +12071,9 @@
       <c r="I239" s="4" t="inlineStr"/>
       <c r="J239" s="4" t="inlineStr"/>
       <c r="K239" s="4" t="inlineStr"/>
-      <c r="L239" s="4" t="inlineStr">
+      <c r="L239" s="4" t="inlineStr"/>
+      <c r="M239" s="4" t="inlineStr"/>
+      <c r="N239" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178265/content.html</t>
         </is>
@@ -11807,7 +12093,7 @@
           <t>重庆市税务局第七稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D240" s="4" t="inlineStr">
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11831,7 +12117,9 @@
       <c r="I240" s="4" t="inlineStr"/>
       <c r="J240" s="4" t="inlineStr"/>
       <c r="K240" s="4" t="inlineStr"/>
-      <c r="L240" s="4" t="inlineStr">
+      <c r="L240" s="4" t="inlineStr"/>
+      <c r="M240" s="4" t="inlineStr"/>
+      <c r="N240" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178223/content.html</t>
         </is>
@@ -11851,7 +12139,7 @@
           <t>江苏省连云港市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D241" s="4" t="inlineStr">
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11875,7 +12163,9 @@
       <c r="I241" s="4" t="inlineStr"/>
       <c r="J241" s="4" t="inlineStr"/>
       <c r="K241" s="4" t="inlineStr"/>
-      <c r="L241" s="4" t="inlineStr">
+      <c r="L241" s="4" t="inlineStr"/>
+      <c r="M241" s="4" t="inlineStr"/>
+      <c r="N241" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178132/content.html</t>
         </is>
@@ -11895,7 +12185,7 @@
           <t>重庆市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D242" s="4" t="inlineStr">
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11919,7 +12209,9 @@
       <c r="I242" s="4" t="inlineStr"/>
       <c r="J242" s="4" t="inlineStr"/>
       <c r="K242" s="4" t="inlineStr"/>
-      <c r="L242" s="4" t="inlineStr">
+      <c r="L242" s="4" t="inlineStr"/>
+      <c r="M242" s="4" t="inlineStr"/>
+      <c r="N242" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5178018/content.html</t>
         </is>
@@ -11939,7 +12231,7 @@
           <t>湖北省孝感市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D243" s="4" t="inlineStr">
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -11963,7 +12255,9 @@
       <c r="I243" s="4" t="inlineStr"/>
       <c r="J243" s="4" t="inlineStr"/>
       <c r="K243" s="4" t="inlineStr"/>
-      <c r="L243" s="4" t="inlineStr">
+      <c r="L243" s="4" t="inlineStr"/>
+      <c r="M243" s="4" t="inlineStr"/>
+      <c r="N243" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177848/content.html</t>
         </is>
@@ -11983,7 +12277,7 @@
           <t>山东省临沂市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D244" s="4" t="inlineStr">
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12007,7 +12301,9 @@
       <c r="I244" s="4" t="inlineStr"/>
       <c r="J244" s="4" t="inlineStr"/>
       <c r="K244" s="4" t="inlineStr"/>
-      <c r="L244" s="4" t="inlineStr">
+      <c r="L244" s="4" t="inlineStr"/>
+      <c r="M244" s="4" t="inlineStr"/>
+      <c r="N244" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177653/content.html</t>
         </is>
@@ -12027,7 +12323,7 @@
           <t>江苏省无锡市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D245" s="4" t="inlineStr">
+      <c r="D245" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12051,7 +12347,9 @@
       <c r="I245" s="4" t="inlineStr"/>
       <c r="J245" s="4" t="inlineStr"/>
       <c r="K245" s="4" t="inlineStr"/>
-      <c r="L245" s="4" t="inlineStr">
+      <c r="L245" s="4" t="inlineStr"/>
+      <c r="M245" s="4" t="inlineStr"/>
+      <c r="N245" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177642/content.html</t>
         </is>
@@ -12071,7 +12369,7 @@
           <t>浙江省嘉兴市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
+      <c r="D246" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12095,7 +12393,9 @@
       <c r="I246" s="4" t="inlineStr"/>
       <c r="J246" s="4" t="inlineStr"/>
       <c r="K246" s="4" t="inlineStr"/>
-      <c r="L246" s="4" t="inlineStr">
+      <c r="L246" s="4" t="inlineStr"/>
+      <c r="M246" s="4" t="inlineStr"/>
+      <c r="N246" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177836/content.html</t>
         </is>
@@ -12115,7 +12415,7 @@
           <t>辽宁省沈阳市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D247" s="4" t="inlineStr">
+      <c r="D247" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12139,7 +12439,9 @@
       <c r="I247" s="4" t="inlineStr"/>
       <c r="J247" s="4" t="inlineStr"/>
       <c r="K247" s="4" t="inlineStr"/>
-      <c r="L247" s="4" t="inlineStr">
+      <c r="L247" s="4" t="inlineStr"/>
+      <c r="M247" s="4" t="inlineStr"/>
+      <c r="N247" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177487/content.html</t>
         </is>
@@ -12159,7 +12461,7 @@
           <t>贵州省遵义市税务局第二稽查局依法查处一起 骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D248" s="4" t="inlineStr">
+      <c r="D248" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12183,7 +12485,9 @@
       <c r="I248" s="4" t="inlineStr"/>
       <c r="J248" s="4" t="inlineStr"/>
       <c r="K248" s="4" t="inlineStr"/>
-      <c r="L248" s="4" t="inlineStr">
+      <c r="L248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="inlineStr"/>
+      <c r="N248" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177157/content.html</t>
         </is>
@@ -12203,7 +12507,7 @@
           <t>广西壮族自治区税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D249" s="4" t="inlineStr">
+      <c r="D249" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12227,7 +12531,9 @@
       <c r="I249" s="4" t="inlineStr"/>
       <c r="J249" s="4" t="inlineStr"/>
       <c r="K249" s="4" t="inlineStr"/>
-      <c r="L249" s="4" t="inlineStr">
+      <c r="L249" s="4" t="inlineStr"/>
+      <c r="M249" s="4" t="inlineStr"/>
+      <c r="N249" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177116/content.html</t>
         </is>
@@ -12247,7 +12553,7 @@
           <t>甘肃省定西市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D250" s="4" t="inlineStr">
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12271,7 +12577,9 @@
       <c r="I250" s="4" t="inlineStr"/>
       <c r="J250" s="4" t="inlineStr"/>
       <c r="K250" s="4" t="inlineStr"/>
-      <c r="L250" s="4" t="inlineStr">
+      <c r="L250" s="4" t="inlineStr"/>
+      <c r="M250" s="4" t="inlineStr"/>
+      <c r="N250" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177061/content.html</t>
         </is>
@@ -12291,7 +12599,7 @@
           <t>湖南省邵阳市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D251" s="4" t="inlineStr">
+      <c r="D251" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12315,7 +12623,9 @@
       <c r="I251" s="4" t="inlineStr"/>
       <c r="J251" s="4" t="inlineStr"/>
       <c r="K251" s="4" t="inlineStr"/>
-      <c r="L251" s="4" t="inlineStr">
+      <c r="L251" s="4" t="inlineStr"/>
+      <c r="M251" s="4" t="inlineStr"/>
+      <c r="N251" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5177053/content.html</t>
         </is>
@@ -12335,7 +12645,7 @@
           <t>辽宁省葫芦岛市税务局稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D252" s="4" t="inlineStr">
+      <c r="D252" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12359,7 +12669,9 @@
       <c r="I252" s="4" t="inlineStr"/>
       <c r="J252" s="4" t="inlineStr"/>
       <c r="K252" s="4" t="inlineStr"/>
-      <c r="L252" s="4" t="inlineStr">
+      <c r="L252" s="4" t="inlineStr"/>
+      <c r="M252" s="4" t="inlineStr"/>
+      <c r="N252" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176991/content.html</t>
         </is>
@@ -12379,7 +12691,7 @@
           <t>厦门市税务局稽查局依法对网络主播范思峰偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D253" s="4" t="inlineStr">
+      <c r="D253" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12401,9 +12713,15 @@
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr"/>
-      <c r="J253" s="4" t="inlineStr"/>
+      <c r="J253" s="6" t="n">
+        <v>167.89</v>
+      </c>
       <c r="K253" s="4" t="inlineStr"/>
-      <c r="L253" s="4" t="inlineStr">
+      <c r="L253" s="4" t="inlineStr"/>
+      <c r="M253" s="6" t="n">
+        <v>649.5</v>
+      </c>
+      <c r="N253" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176956/content.html</t>
         </is>
@@ -12423,7 +12741,7 @@
           <t>江苏省宿迁市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D254" s="4" t="inlineStr">
+      <c r="D254" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12447,7 +12765,9 @@
       <c r="I254" s="4" t="inlineStr"/>
       <c r="J254" s="4" t="inlineStr"/>
       <c r="K254" s="4" t="inlineStr"/>
-      <c r="L254" s="4" t="inlineStr">
+      <c r="L254" s="4" t="inlineStr"/>
+      <c r="M254" s="4" t="inlineStr"/>
+      <c r="N254" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176942/content.html</t>
         </is>
@@ -12467,7 +12787,7 @@
           <t>重庆市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D255" s="4" t="inlineStr">
+      <c r="D255" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12491,7 +12811,9 @@
       <c r="I255" s="4" t="inlineStr"/>
       <c r="J255" s="4" t="inlineStr"/>
       <c r="K255" s="4" t="inlineStr"/>
-      <c r="L255" s="4" t="inlineStr">
+      <c r="L255" s="4" t="inlineStr"/>
+      <c r="M255" s="4" t="inlineStr"/>
+      <c r="N255" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176789/content.html</t>
         </is>
@@ -12511,7 +12833,7 @@
           <t>甘肃省甘南藏族自治州税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D256" s="4" t="inlineStr">
+      <c r="D256" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12535,7 +12857,9 @@
       <c r="I256" s="4" t="inlineStr"/>
       <c r="J256" s="4" t="inlineStr"/>
       <c r="K256" s="4" t="inlineStr"/>
-      <c r="L256" s="4" t="inlineStr">
+      <c r="L256" s="4" t="inlineStr"/>
+      <c r="M256" s="4" t="inlineStr"/>
+      <c r="N256" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176751/content.html</t>
         </is>
@@ -12555,7 +12879,7 @@
           <t>浙江省金华市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D257" s="4" t="inlineStr">
+      <c r="D257" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12579,7 +12903,9 @@
       <c r="I257" s="4" t="inlineStr"/>
       <c r="J257" s="4" t="inlineStr"/>
       <c r="K257" s="4" t="inlineStr"/>
-      <c r="L257" s="4" t="inlineStr">
+      <c r="L257" s="4" t="inlineStr"/>
+      <c r="M257" s="4" t="inlineStr"/>
+      <c r="N257" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176738/content.html</t>
         </is>
@@ -12599,7 +12925,7 @@
           <t>河北省廊坊市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D258" s="4" t="inlineStr">
+      <c r="D258" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12623,7 +12949,9 @@
       <c r="I258" s="4" t="inlineStr"/>
       <c r="J258" s="4" t="inlineStr"/>
       <c r="K258" s="4" t="inlineStr"/>
-      <c r="L258" s="4" t="inlineStr">
+      <c r="L258" s="4" t="inlineStr"/>
+      <c r="M258" s="4" t="inlineStr"/>
+      <c r="N258" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176729/content.html</t>
         </is>
@@ -12643,7 +12971,7 @@
           <t>安徽省合肥市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D259" s="4" t="inlineStr">
+      <c r="D259" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12667,7 +12995,9 @@
       <c r="I259" s="4" t="inlineStr"/>
       <c r="J259" s="4" t="inlineStr"/>
       <c r="K259" s="4" t="inlineStr"/>
-      <c r="L259" s="4" t="inlineStr">
+      <c r="L259" s="4" t="inlineStr"/>
+      <c r="M259" s="4" t="inlineStr"/>
+      <c r="N259" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176641/content.html</t>
         </is>
@@ -12687,7 +13017,7 @@
           <t>广东省江门市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D260" s="4" t="inlineStr">
+      <c r="D260" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12711,7 +13041,9 @@
       <c r="I260" s="4" t="inlineStr"/>
       <c r="J260" s="4" t="inlineStr"/>
       <c r="K260" s="4" t="inlineStr"/>
-      <c r="L260" s="4" t="inlineStr">
+      <c r="L260" s="4" t="inlineStr"/>
+      <c r="M260" s="4" t="inlineStr"/>
+      <c r="N260" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176515/content.html</t>
         </is>
@@ -12731,7 +13063,7 @@
           <t>甘肃省白银市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D261" s="4" t="inlineStr">
+      <c r="D261" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12755,7 +13087,9 @@
       <c r="I261" s="4" t="inlineStr"/>
       <c r="J261" s="4" t="inlineStr"/>
       <c r="K261" s="4" t="inlineStr"/>
-      <c r="L261" s="4" t="inlineStr">
+      <c r="L261" s="4" t="inlineStr"/>
+      <c r="M261" s="4" t="inlineStr"/>
+      <c r="N261" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176389/content.html</t>
         </is>
@@ -12775,7 +13109,7 @@
           <t>湖南省永州市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D262" s="4" t="inlineStr">
+      <c r="D262" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12799,7 +13133,9 @@
       <c r="I262" s="4" t="inlineStr"/>
       <c r="J262" s="4" t="inlineStr"/>
       <c r="K262" s="4" t="inlineStr"/>
-      <c r="L262" s="4" t="inlineStr">
+      <c r="L262" s="4" t="inlineStr"/>
+      <c r="M262" s="4" t="inlineStr"/>
+      <c r="N262" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176376/content.html</t>
         </is>
@@ -12819,7 +13155,7 @@
           <t>天津市税务局第四稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D263" s="4" t="inlineStr">
+      <c r="D263" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12843,7 +13179,9 @@
       <c r="I263" s="4" t="inlineStr"/>
       <c r="J263" s="4" t="inlineStr"/>
       <c r="K263" s="4" t="inlineStr"/>
-      <c r="L263" s="4" t="inlineStr">
+      <c r="L263" s="4" t="inlineStr"/>
+      <c r="M263" s="4" t="inlineStr"/>
+      <c r="N263" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176221/content.html</t>
         </is>
@@ -12863,7 +13201,7 @@
           <t>江西省抚州市税务局依法对网络主播徐国豪偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D264" s="4" t="inlineStr">
+      <c r="D264" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12889,9 +13227,15 @@
         </is>
       </c>
       <c r="I264" s="4" t="inlineStr"/>
-      <c r="J264" s="4" t="inlineStr"/>
+      <c r="J264" s="6" t="n">
+        <v>1755.57</v>
+      </c>
       <c r="K264" s="4" t="inlineStr"/>
-      <c r="L264" s="4" t="inlineStr">
+      <c r="L264" s="4" t="inlineStr"/>
+      <c r="M264" s="6" t="n">
+        <v>10800</v>
+      </c>
+      <c r="N264" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176210/content.html</t>
         </is>
@@ -12911,7 +13255,7 @@
           <t>河北省张家口市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D265" s="4" t="inlineStr">
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12935,7 +13279,9 @@
       <c r="I265" s="4" t="inlineStr"/>
       <c r="J265" s="4" t="inlineStr"/>
       <c r="K265" s="4" t="inlineStr"/>
-      <c r="L265" s="4" t="inlineStr">
+      <c r="L265" s="4" t="inlineStr"/>
+      <c r="M265" s="4" t="inlineStr"/>
+      <c r="N265" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176175/content.html</t>
         </is>
@@ -12955,7 +13301,7 @@
           <t>天津市税务局第一稽查局依法查处两起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D266" s="4" t="inlineStr">
+      <c r="D266" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -12979,7 +13325,9 @@
       <c r="I266" s="4" t="inlineStr"/>
       <c r="J266" s="4" t="inlineStr"/>
       <c r="K266" s="4" t="inlineStr"/>
-      <c r="L266" s="4" t="inlineStr">
+      <c r="L266" s="4" t="inlineStr"/>
+      <c r="M266" s="4" t="inlineStr"/>
+      <c r="N266" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176072/content.html</t>
         </is>
@@ -12999,7 +13347,7 @@
           <t>北京市税务局第四稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D267" s="4" t="inlineStr">
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13023,7 +13371,9 @@
       <c r="I267" s="4" t="inlineStr"/>
       <c r="J267" s="4" t="inlineStr"/>
       <c r="K267" s="4" t="inlineStr"/>
-      <c r="L267" s="4" t="inlineStr">
+      <c r="L267" s="4" t="inlineStr"/>
+      <c r="M267" s="4" t="inlineStr"/>
+      <c r="N267" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176032/content.html</t>
         </is>
@@ -13043,7 +13393,7 @@
           <t>天津市税务局稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D268" s="4" t="inlineStr">
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13067,7 +13417,9 @@
       <c r="I268" s="4" t="inlineStr"/>
       <c r="J268" s="4" t="inlineStr"/>
       <c r="K268" s="4" t="inlineStr"/>
-      <c r="L268" s="4" t="inlineStr">
+      <c r="L268" s="4" t="inlineStr"/>
+      <c r="M268" s="4" t="inlineStr"/>
+      <c r="N268" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176031/content.html</t>
         </is>
@@ -13087,7 +13439,7 @@
           <t>贵州省黔西南布依族苗族自治州税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D269" s="4" t="inlineStr">
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13111,7 +13463,9 @@
       <c r="I269" s="4" t="inlineStr"/>
       <c r="J269" s="4" t="inlineStr"/>
       <c r="K269" s="4" t="inlineStr"/>
-      <c r="L269" s="4" t="inlineStr">
+      <c r="L269" s="4" t="inlineStr"/>
+      <c r="M269" s="4" t="inlineStr"/>
+      <c r="N269" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5176019/content.html</t>
         </is>
@@ -13131,7 +13485,7 @@
           <t>山东省潍坊市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D270" s="4" t="inlineStr">
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13155,7 +13509,9 @@
       <c r="I270" s="4" t="inlineStr"/>
       <c r="J270" s="4" t="inlineStr"/>
       <c r="K270" s="4" t="inlineStr"/>
-      <c r="L270" s="4" t="inlineStr">
+      <c r="L270" s="4" t="inlineStr"/>
+      <c r="M270" s="4" t="inlineStr"/>
+      <c r="N270" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175981/content.html</t>
         </is>
@@ -13175,7 +13531,7 @@
           <t>北京市税务局第二稽查局依法对网络主播孙自烜偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D271" s="4" t="inlineStr">
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13201,9 +13557,15 @@
         </is>
       </c>
       <c r="I271" s="4" t="inlineStr"/>
-      <c r="J271" s="4" t="inlineStr"/>
+      <c r="J271" s="6" t="n">
+        <v>197.86</v>
+      </c>
       <c r="K271" s="4" t="inlineStr"/>
-      <c r="L271" s="4" t="inlineStr">
+      <c r="L271" s="4" t="inlineStr"/>
+      <c r="M271" s="6" t="n">
+        <v>1171.45</v>
+      </c>
+      <c r="N271" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175965/content.html</t>
         </is>
@@ -13223,7 +13585,7 @@
           <t>浙江省台州市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D272" s="4" t="inlineStr">
+      <c r="D272" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13247,7 +13609,9 @@
       <c r="I272" s="4" t="inlineStr"/>
       <c r="J272" s="4" t="inlineStr"/>
       <c r="K272" s="4" t="inlineStr"/>
-      <c r="L272" s="4" t="inlineStr">
+      <c r="L272" s="4" t="inlineStr"/>
+      <c r="M272" s="4" t="inlineStr"/>
+      <c r="N272" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175883/content.html</t>
         </is>
@@ -13267,7 +13631,7 @@
           <t>贵州省遵义市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D273" s="4" t="inlineStr">
+      <c r="D273" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13291,7 +13655,9 @@
       <c r="I273" s="4" t="inlineStr"/>
       <c r="J273" s="4" t="inlineStr"/>
       <c r="K273" s="4" t="inlineStr"/>
-      <c r="L273" s="4" t="inlineStr">
+      <c r="L273" s="4" t="inlineStr"/>
+      <c r="M273" s="4" t="inlineStr"/>
+      <c r="N273" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175861/content.html</t>
         </is>
@@ -13311,7 +13677,7 @@
           <t>厦门市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D274" s="4" t="inlineStr">
+      <c r="D274" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13331,7 +13697,9 @@
       <c r="I274" s="4" t="inlineStr"/>
       <c r="J274" s="4" t="inlineStr"/>
       <c r="K274" s="4" t="inlineStr"/>
-      <c r="L274" s="4" t="inlineStr">
+      <c r="L274" s="4" t="inlineStr"/>
+      <c r="M274" s="4" t="inlineStr"/>
+      <c r="N274" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175855/content.html</t>
         </is>
@@ -13351,7 +13719,7 @@
           <t>青海省海西蒙古族藏族自治州税务局稽查局依法查处一起商贸企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D275" s="4" t="inlineStr">
+      <c r="D275" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13375,7 +13743,9 @@
       <c r="I275" s="4" t="inlineStr"/>
       <c r="J275" s="4" t="inlineStr"/>
       <c r="K275" s="4" t="inlineStr"/>
-      <c r="L275" s="4" t="inlineStr">
+      <c r="L275" s="4" t="inlineStr"/>
+      <c r="M275" s="4" t="inlineStr"/>
+      <c r="N275" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175841/content.html</t>
         </is>
@@ -13395,7 +13765,7 @@
           <t>海南省税务部门依法查处一起商贸企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D276" s="4" t="inlineStr">
+      <c r="D276" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13419,7 +13789,9 @@
       <c r="I276" s="4" t="inlineStr"/>
       <c r="J276" s="4" t="inlineStr"/>
       <c r="K276" s="4" t="inlineStr"/>
-      <c r="L276" s="4" t="inlineStr">
+      <c r="L276" s="4" t="inlineStr"/>
+      <c r="M276" s="4" t="inlineStr"/>
+      <c r="N276" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175732/content.html</t>
         </is>
@@ -13439,7 +13811,7 @@
           <t>黑龙江省绥化市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D277" s="4" t="inlineStr">
+      <c r="D277" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13463,7 +13835,9 @@
       <c r="I277" s="4" t="inlineStr"/>
       <c r="J277" s="4" t="inlineStr"/>
       <c r="K277" s="4" t="inlineStr"/>
-      <c r="L277" s="4" t="inlineStr">
+      <c r="L277" s="4" t="inlineStr"/>
+      <c r="M277" s="4" t="inlineStr"/>
+      <c r="N277" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175698/content.html</t>
         </is>
@@ -13483,7 +13857,7 @@
           <t>宁夏回族自治区税务部门依法查处一起工贸企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D278" s="4" t="inlineStr">
+      <c r="D278" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13507,7 +13881,9 @@
       <c r="I278" s="4" t="inlineStr"/>
       <c r="J278" s="4" t="inlineStr"/>
       <c r="K278" s="4" t="inlineStr"/>
-      <c r="L278" s="4" t="inlineStr">
+      <c r="L278" s="4" t="inlineStr"/>
+      <c r="M278" s="4" t="inlineStr"/>
+      <c r="N278" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175689/content.html</t>
         </is>
@@ -13527,7 +13903,7 @@
           <t>北京市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D279" s="4" t="inlineStr">
+      <c r="D279" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13551,7 +13927,9 @@
       <c r="I279" s="4" t="inlineStr"/>
       <c r="J279" s="4" t="inlineStr"/>
       <c r="K279" s="4" t="inlineStr"/>
-      <c r="L279" s="4" t="inlineStr">
+      <c r="L279" s="4" t="inlineStr"/>
+      <c r="M279" s="4" t="inlineStr"/>
+      <c r="N279" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175658/content.html</t>
         </is>
@@ -13571,7 +13949,7 @@
           <t>大连市税务局第二稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D280" s="4" t="inlineStr">
+      <c r="D280" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13591,7 +13969,9 @@
       <c r="I280" s="4" t="inlineStr"/>
       <c r="J280" s="4" t="inlineStr"/>
       <c r="K280" s="4" t="inlineStr"/>
-      <c r="L280" s="4" t="inlineStr">
+      <c r="L280" s="4" t="inlineStr"/>
+      <c r="M280" s="4" t="inlineStr"/>
+      <c r="N280" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175655/content.html</t>
         </is>
@@ -13611,7 +13991,7 @@
           <t>重庆市税务局第八稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D281" s="4" t="inlineStr">
+      <c r="D281" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13635,7 +14015,9 @@
       <c r="I281" s="4" t="inlineStr"/>
       <c r="J281" s="4" t="inlineStr"/>
       <c r="K281" s="4" t="inlineStr"/>
-      <c r="L281" s="4" t="inlineStr">
+      <c r="L281" s="4" t="inlineStr"/>
+      <c r="M281" s="4" t="inlineStr"/>
+      <c r="N281" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175610/content.html</t>
         </is>
@@ -13655,7 +14037,7 @@
           <t>辽宁省抚顺市税务部门依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D282" s="4" t="inlineStr">
+      <c r="D282" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13679,7 +14061,9 @@
       <c r="I282" s="4" t="inlineStr"/>
       <c r="J282" s="4" t="inlineStr"/>
       <c r="K282" s="4" t="inlineStr"/>
-      <c r="L282" s="4" t="inlineStr">
+      <c r="L282" s="4" t="inlineStr"/>
+      <c r="M282" s="4" t="inlineStr"/>
+      <c r="N282" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175585/content.html</t>
         </is>
@@ -13699,7 +14083,7 @@
           <t>青岛市税务局第二稽查局依法查处一起商贸企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D283" s="4" t="inlineStr">
+      <c r="D283" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13719,7 +14103,9 @@
       <c r="I283" s="4" t="inlineStr"/>
       <c r="J283" s="4" t="inlineStr"/>
       <c r="K283" s="4" t="inlineStr"/>
-      <c r="L283" s="4" t="inlineStr">
+      <c r="L283" s="4" t="inlineStr"/>
+      <c r="M283" s="4" t="inlineStr"/>
+      <c r="N283" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175550/content.html</t>
         </is>
@@ -13739,7 +14125,7 @@
           <t>厦门市税务局第一稽查局依法查处一起汽车销售服务企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D284" s="4" t="inlineStr">
+      <c r="D284" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13759,7 +14145,9 @@
       <c r="I284" s="4" t="inlineStr"/>
       <c r="J284" s="4" t="inlineStr"/>
       <c r="K284" s="4" t="inlineStr"/>
-      <c r="L284" s="4" t="inlineStr">
+      <c r="L284" s="4" t="inlineStr"/>
+      <c r="M284" s="4" t="inlineStr"/>
+      <c r="N284" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175527/content.html</t>
         </is>
@@ -13779,7 +14167,7 @@
           <t>青海省海西蒙古族藏族自治州税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D285" s="4" t="inlineStr">
+      <c r="D285" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13803,7 +14191,9 @@
       <c r="I285" s="4" t="inlineStr"/>
       <c r="J285" s="4" t="inlineStr"/>
       <c r="K285" s="4" t="inlineStr"/>
-      <c r="L285" s="4" t="inlineStr">
+      <c r="L285" s="4" t="inlineStr"/>
+      <c r="M285" s="4" t="inlineStr"/>
+      <c r="N285" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175507/content.html</t>
         </is>
@@ -13823,7 +14213,7 @@
           <t>辽宁省税务部门依法查处一起商贸企业骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D286" s="4" t="inlineStr">
+      <c r="D286" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13847,7 +14237,9 @@
       <c r="I286" s="4" t="inlineStr"/>
       <c r="J286" s="4" t="inlineStr"/>
       <c r="K286" s="4" t="inlineStr"/>
-      <c r="L286" s="4" t="inlineStr">
+      <c r="L286" s="4" t="inlineStr"/>
+      <c r="M286" s="4" t="inlineStr"/>
+      <c r="N286" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175472/content.html</t>
         </is>
@@ -13867,7 +14259,7 @@
           <t>山东省聊城市税务局第一稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D287" s="4" t="inlineStr">
+      <c r="D287" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13891,7 +14283,9 @@
       <c r="I287" s="4" t="inlineStr"/>
       <c r="J287" s="4" t="inlineStr"/>
       <c r="K287" s="4" t="inlineStr"/>
-      <c r="L287" s="4" t="inlineStr">
+      <c r="L287" s="4" t="inlineStr"/>
+      <c r="M287" s="4" t="inlineStr"/>
+      <c r="N287" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175392/content.html</t>
         </is>
@@ -13911,7 +14305,7 @@
           <t>青岛市税务局第三稽查局依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D288" s="4" t="inlineStr">
+      <c r="D288" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13931,7 +14325,9 @@
       <c r="I288" s="4" t="inlineStr"/>
       <c r="J288" s="4" t="inlineStr"/>
       <c r="K288" s="4" t="inlineStr"/>
-      <c r="L288" s="4" t="inlineStr">
+      <c r="L288" s="4" t="inlineStr"/>
+      <c r="M288" s="4" t="inlineStr"/>
+      <c r="N288" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175358/content.html</t>
         </is>
@@ -13951,7 +14347,7 @@
           <t>贵州省安顺市税务部门依法查处一起骗取留抵退税案件</t>
         </is>
       </c>
-      <c r="D289" s="4" t="inlineStr">
+      <c r="D289" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -13975,7 +14371,9 @@
       <c r="I289" s="4" t="inlineStr"/>
       <c r="J289" s="4" t="inlineStr"/>
       <c r="K289" s="4" t="inlineStr"/>
-      <c r="L289" s="4" t="inlineStr">
+      <c r="L289" s="4" t="inlineStr"/>
+      <c r="M289" s="4" t="inlineStr"/>
+      <c r="N289" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175336/content.html</t>
         </is>
@@ -14015,7 +14413,9 @@
       <c r="I290" s="4" t="inlineStr"/>
       <c r="J290" s="4" t="inlineStr"/>
       <c r="K290" s="4" t="inlineStr"/>
-      <c r="L290" s="4" t="inlineStr">
+      <c r="L290" s="4" t="inlineStr"/>
+      <c r="M290" s="4" t="inlineStr"/>
+      <c r="N290" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5175238/content.html</t>
         </is>
@@ -14035,7 +14435,7 @@
           <t>上海市税务局第四稽查局依法对邓伦偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D291" s="4" t="inlineStr">
+      <c r="D291" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14061,9 +14461,15 @@
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr"/>
-      <c r="J291" s="4" t="inlineStr"/>
+      <c r="J291" s="6" t="n">
+        <v>4765.82</v>
+      </c>
       <c r="K291" s="4" t="inlineStr"/>
-      <c r="L291" s="4" t="inlineStr">
+      <c r="L291" s="4" t="inlineStr"/>
+      <c r="M291" s="6" t="n">
+        <v>10600</v>
+      </c>
+      <c r="N291" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5173576/content.html</t>
         </is>
@@ -14083,7 +14489,7 @@
           <t>安徽省安庆市税务部门依法查处一起虚开增值税专用发票案</t>
         </is>
       </c>
-      <c r="D292" s="4" t="inlineStr">
+      <c r="D292" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14107,7 +14513,9 @@
       <c r="I292" s="4" t="inlineStr"/>
       <c r="J292" s="4" t="inlineStr"/>
       <c r="K292" s="4" t="inlineStr"/>
-      <c r="L292" s="4" t="inlineStr">
+      <c r="L292" s="4" t="inlineStr"/>
+      <c r="M292" s="4" t="inlineStr"/>
+      <c r="N292" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5173574/content.html</t>
         </is>
@@ -14127,7 +14535,7 @@
           <t>广东省广州市税务部门依法对网络主播平荣偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D293" s="4" t="inlineStr">
+      <c r="D293" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14153,9 +14561,15 @@
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr"/>
-      <c r="J293" s="4" t="inlineStr"/>
+      <c r="J293" s="6" t="n">
+        <v>1926.05</v>
+      </c>
       <c r="K293" s="4" t="inlineStr"/>
-      <c r="L293" s="4" t="inlineStr">
+      <c r="L293" s="4" t="inlineStr"/>
+      <c r="M293" s="6" t="n">
+        <v>6200.3</v>
+      </c>
+      <c r="N293" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5172913/content.html</t>
         </is>
@@ -14175,7 +14589,7 @@
           <t>深圳市税务部门依法查处一起中介涉税违法案件</t>
         </is>
       </c>
-      <c r="D294" s="4" t="inlineStr">
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14195,7 +14609,9 @@
       <c r="I294" s="4" t="inlineStr"/>
       <c r="J294" s="4" t="inlineStr"/>
       <c r="K294" s="4" t="inlineStr"/>
-      <c r="L294" s="4" t="inlineStr">
+      <c r="L294" s="4" t="inlineStr"/>
+      <c r="M294" s="4" t="inlineStr"/>
+      <c r="N294" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5172911/content.html</t>
         </is>
@@ -14215,7 +14631,7 @@
           <t>山东省济南市税务部门依法查处一起虚开机动车发票案</t>
         </is>
       </c>
-      <c r="D295" s="4" t="inlineStr">
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14239,7 +14655,9 @@
       <c r="I295" s="4" t="inlineStr"/>
       <c r="J295" s="4" t="inlineStr"/>
       <c r="K295" s="4" t="inlineStr"/>
-      <c r="L295" s="4" t="inlineStr">
+      <c r="L295" s="4" t="inlineStr"/>
+      <c r="M295" s="4" t="inlineStr"/>
+      <c r="N295" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5172810/content.html</t>
         </is>
@@ -14259,7 +14677,7 @@
           <t>广西河池市税务部门依法查处一起中介涉税违法案件</t>
         </is>
       </c>
-      <c r="D296" s="4" t="inlineStr">
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14283,7 +14701,9 @@
       <c r="I296" s="4" t="inlineStr"/>
       <c r="J296" s="4" t="inlineStr"/>
       <c r="K296" s="4" t="inlineStr"/>
-      <c r="L296" s="4" t="inlineStr">
+      <c r="L296" s="4" t="inlineStr"/>
+      <c r="M296" s="4" t="inlineStr"/>
+      <c r="N296" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5172443/content.html</t>
         </is>
@@ -14327,7 +14747,9 @@
       <c r="I297" s="4" t="inlineStr"/>
       <c r="J297" s="4" t="inlineStr"/>
       <c r="K297" s="4" t="inlineStr"/>
-      <c r="L297" s="4" t="inlineStr">
+      <c r="L297" s="4" t="inlineStr"/>
+      <c r="M297" s="4" t="inlineStr"/>
+      <c r="N297" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5172245/content.html</t>
         </is>
@@ -14371,7 +14793,9 @@
       <c r="I298" s="4" t="inlineStr"/>
       <c r="J298" s="4" t="inlineStr"/>
       <c r="K298" s="4" t="inlineStr"/>
-      <c r="L298" s="4" t="inlineStr">
+      <c r="L298" s="4" t="inlineStr"/>
+      <c r="M298" s="4" t="inlineStr"/>
+      <c r="N298" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5171508/content.html</t>
         </is>
@@ -14391,7 +14815,7 @@
           <t>浙江省杭州市税务部门依法对黄薇偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D299" s="4" t="inlineStr">
+      <c r="D299" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14417,9 +14841,15 @@
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr"/>
-      <c r="J299" s="4" t="inlineStr"/>
+      <c r="J299" s="6" t="n">
+        <v>64300</v>
+      </c>
       <c r="K299" s="4" t="inlineStr"/>
-      <c r="L299" s="4" t="inlineStr">
+      <c r="L299" s="4" t="inlineStr"/>
+      <c r="M299" s="6" t="n">
+        <v>134100</v>
+      </c>
+      <c r="N299" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5171507/content.html</t>
         </is>
@@ -14439,7 +14869,7 @@
           <t>浙江省杭州市税务部门依法对朱宸慧、林珊珊偷逃税案件进行处理</t>
         </is>
       </c>
-      <c r="D300" s="4" t="inlineStr">
+      <c r="D300" s="5" t="inlineStr">
         <is>
           <t>执法通报</t>
         </is>
@@ -14467,17 +14897,21 @@
       <c r="I300" s="4" t="inlineStr"/>
       <c r="J300" s="4" t="inlineStr"/>
       <c r="K300" s="4" t="inlineStr"/>
-      <c r="L300" s="4" t="inlineStr">
+      <c r="L300" s="4" t="inlineStr"/>
+      <c r="M300" s="6" t="n">
+        <v>6555.31</v>
+      </c>
+      <c r="N300" s="4" t="inlineStr">
         <is>
           <t>http://www.chinatax.gov.cn/chinatax/n810219/c102025/c5170767/content.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L300"/>
+  <autoFilter ref="A3:N300"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14489,79 +14923,1142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>数据</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>案件</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>税款(万)</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>罚款(万)</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>滞纳金(万)</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>合计(万)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总案件</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>297</v>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>税务部门再曝光6起加油站偷税案件 依法查处隐匿收入偷税行为 坚决维护税收法治公平</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr"/>
+      <c r="C2" s="9" t="inlineStr"/>
+      <c r="D2" s="9" t="inlineStr"/>
+      <c r="E2" s="10" t="n">
+        <v>294300</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>有金额</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>63</v>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>浙江省杭州市税务部门依法对黄薇偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>64300</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr"/>
+      <c r="E3" s="10" t="n">
+        <v>134100</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>有涉案人</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>131</v>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局西安市税务局第三稽查局联合公安机关依法查处网络货运平台运是滴科技发展有限责任公司虚开增值</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr"/>
+      <c r="C4" s="9" t="inlineStr"/>
+      <c r="D4" s="9" t="inlineStr"/>
+      <c r="E4" s="10" t="n">
+        <v>130400</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>有涉案企业</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>103</v>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>广西壮族自治区玉林市警税联合依法查处一起ETC通行费电子发票虚开案件</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr"/>
+      <c r="C5" s="9" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="10" t="n">
+        <v>51600</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>有省份</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>171</v>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>湖南省娄底市税务部门联合公安机关依法查处涉税中介涟源市娄涟财务管理有限公司及其实际控制人谢久华勾结税</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="10" t="n">
+        <v>26000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>有税务机关</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>136</v>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局牡丹江市税务局依法查处一起代理办税人员与税务人员勾连勾兑虚开增值税专用发票案件</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="10" t="n">
+        <v>25300</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>山东省税务局稽查局依法查处一起成品油生产企业偷税案件</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="10" t="n">
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>税务部门曝光4起社会教育培训行业偷税案件 私账收款、少计收入、骗享优惠等违法行为被依法查处</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="10" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>山西省阳泉市税警联合依法查处涉税中介阳泉市易创商务服务有限公司及其实际控制人任宇宙虚开增值税专用发票</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="10" t="n">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>云南省文山壮族苗族自治州警税联合依法查处一起虚开农产品收购发票案件</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="10" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>天津税务部门联合公安机关依法查处涉税中介 天津畅泽财务管理有限公司及其实际控制人张凤梅虚开增值税发票</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="10" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>内蒙古兴安盟税警联合依法查处涉税中介兴安盟中呈财务咨询有限公司及其法定代表人倪冬雪虚开增值税发票案件</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="10" t="n">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>江西省抚州市税务局依法对网络主播徐国豪偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>1755.57</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="10" t="n">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>上海市税务局第一稽查局依法查处一起机动车销售企业偷税案件</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="10" t="n">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>上海市税务局第四稽查局依法对邓伦偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>4765.82</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="10" t="n">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>浙江省杭州市税务部门依法对朱宸慧、林珊珊偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="10" t="n">
+        <v>6555.31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>广东省广州市税务部门依法对网络主播平荣偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1926.05</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="10" t="n">
+        <v>6200.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>辽宁省抚顺市税警联合依法查处一起涉税中介机构涉嫌组织虚开发票帮助他人偷逃税款案件</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>5379</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="10" t="n">
+        <v>5379</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局深圳市税务局稽查局依法查处涉税中介深圳市财智恒通企业管理咨询有限公司非法提供银行账户和发</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="10" t="n">
+        <v>4792.11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局深圳市税务局稽查局依法查处深圳金斯达应用材料有限公司骗享研发费用加计扣除税收优惠偷税案件</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>1621.16</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="10" t="n">
+        <v>3618.15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>浙江省多部门联合依法查处一起骗取出口退税团伙案件</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="10" t="n">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局大连市税务局第一稽查局依法查处涉税中介大连市澎源财税管理咨询有限公司介绍虚开发票造成其代</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="10" t="n">
+        <v>2736.04</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>退税“馅饼”实为“陷阱” 近1800人上当受骗——咸阳税警联合依法查处一起诱导纳税人虚假填报个人所得</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="10" t="n">
+        <v>1573.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局咸阳市税务局联合公安机关依法查处“黑中介”诱导纳税人虚假填报个人所得税专项附加扣除骗取退</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="10" t="n">
+        <v>1573.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>广西壮族自治区税务局第三稽查局依法对网络主播吴川偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>827.91</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="10" t="n">
+        <v>1359.08</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>山西省吕梁市税务局稽查局依法查处一起虚报研发费用加计扣除偷税案件</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>796</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr"/>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="10" t="n">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局海南省税务局第一稽查局依法查处欧丽家公司隐匿未开票收入偷税案件</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr"/>
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="10" t="n">
+        <v>1256.98</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>北京市税务局第二稽查局依法对网络主播孙自烜偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>197.86</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr"/>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="10" t="n">
+        <v>1171.45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局安顺市税务局稽查局依法查处涉税中介贵州理得清财务有限公司介绍虚开增值税专用发票造成其代理</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="10" t="n">
+        <v>937.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>税务部门依法查处“探店”网红白冰偷税案件 税款、滞纳金、罚款1891万元已入库</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr"/>
+      <c r="C31" s="10" t="n">
+        <v>1891</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="10" t="n">
+        <v>911.1799999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>四川省泸州市税务局稽查局依法对网络主播余洋偷税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="10" t="n">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局图木舒克税务局依法对东城迎宾加油加气站偷税案进行处理</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="10" t="n">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局上海市税务局第三稽查局依法对网络主播王子柏偷税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="10" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>税务总局驻沈阳特派办组织辽宁省营口市税务局稽查局依法对网络主播田小龙偷税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="10" t="n">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局鹤壁市税务局稽查局依法查处鹤壁市国用商贸有限公司偷税案件</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="10" t="n">
+        <v>678.72</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局长治市税务局稽查局依法查处潞城市雨田实业有限责任公司第一加油站偷税案件</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr"/>
+      <c r="C37" s="9" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="10" t="n">
+        <v>662.45</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>大连市税务局第一稽查局依法对网络主播王纯善偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>218.3</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="10" t="n">
+        <v>653.61</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>厦门市税务局稽查局依法对网络主播范思峰偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>167.89</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="10" t="n">
+        <v>649.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>贵州省税务等多部门联合依法查处一起骗取出口退税案件</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr"/>
+      <c r="C40" s="9" t="inlineStr"/>
+      <c r="D40" s="9" t="inlineStr"/>
+      <c r="E40" s="10" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局嘉兴市税务局第一稽查局依法查处嘉善景盛混凝土制品有限公司骗享研发费用加计扣除</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr"/>
+      <c r="C41" s="9" t="inlineStr"/>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="10" t="n">
+        <v>609.14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局稽查局依法查处涉税中介福州金汇鑫财税咨询有限公司帮助其代理企业骗取出口退税案</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr"/>
+      <c r="C42" s="9" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="10" t="n">
+        <v>564.5700000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局邯郸市税务局稽查局依法查处邯郸市丛台区群帮耐火材料厂隐匿出口应征税货物收入偷税案件</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr"/>
+      <c r="C43" s="9" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="10" t="n">
+        <v>550.91</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>厦门市税务局稽查局依法对网络主播姚振宇偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>236.3</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="10" t="n">
+        <v>545.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局宁波市税务局第三稽查局依法查处夏安阳拆分收入骗享个人所得税税收优惠偷税案件</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr"/>
+      <c r="C45" s="9" t="inlineStr"/>
+      <c r="D45" s="9" t="inlineStr"/>
+      <c r="E45" s="10" t="n">
+        <v>518.88</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>安徽省宿州市税务局稽查局依法对网络主播吴思豪少缴税款案进行处理</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>210.57</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr"/>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="10" t="n">
+        <v>476.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局黔东南州税务局稽查局依法查处凯里市个体工商户业主项祖顺拆分收入骗享小规模纳税人税费优惠偷</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr"/>
+      <c r="C47" s="9" t="inlineStr"/>
+      <c r="D47" s="9" t="inlineStr"/>
+      <c r="E47" s="10" t="n">
+        <v>445.28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局文山州税务局第二稽查局依法对丘北县树皮岔路加油站偷税案进行处理</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr"/>
+      <c r="C48" s="9" t="inlineStr"/>
+      <c r="D48" s="9" t="inlineStr"/>
+      <c r="E48" s="10" t="n">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局福州市税务局第二稽查局依法查处福州晋安区德乐加乐贸易有限公司拒不申报出口货物应征税偷税案</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr"/>
+      <c r="C49" s="9" t="inlineStr"/>
+      <c r="D49" s="9" t="inlineStr"/>
+      <c r="E49" s="10" t="n">
+        <v>402.28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局沈阳市税务局第三稽查局依法查处网络主播李呈祥偷税案件</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr"/>
+      <c r="C50" s="9" t="inlineStr"/>
+      <c r="D50" s="9" t="inlineStr"/>
+      <c r="E50" s="10" t="n">
+        <v>402.14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>安徽省滁州市税警联合依法查处涉税中介安徽盛乾会计服务有限公司及其实际控制人胡洋虚开增值税专用发票案件</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr"/>
+      <c r="C51" s="9" t="inlineStr"/>
+      <c r="D51" s="9" t="inlineStr"/>
+      <c r="E51" s="10" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局安顺市税务局第一稽查局依法查处安顺市百年婚宴有限公司利用关联个体工商户拆分收入偷税案件</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr"/>
+      <c r="C52" s="9" t="inlineStr"/>
+      <c r="D52" s="9" t="inlineStr"/>
+      <c r="E52" s="10" t="n">
+        <v>392.79</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>河南省税务部门依法查处一起加油站偷税案件</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr"/>
+      <c r="D53" s="9" t="inlineStr"/>
+      <c r="E53" s="10" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>河南省洛阳市税务局稽查局依法对网络主播马海涛、梁娜偷税案进行处理</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr"/>
+      <c r="C54" s="9" t="inlineStr"/>
+      <c r="D54" s="9" t="inlineStr"/>
+      <c r="E54" s="10" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局三明市税务局稽查局依法查处自然人王元春、王逢春偷税案件</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr"/>
+      <c r="C55" s="9" t="inlineStr"/>
+      <c r="D55" s="9" t="inlineStr"/>
+      <c r="E55" s="10" t="n">
+        <v>298.29</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>重庆市税务局第七稽查局依法对袁冰妍及其关联企业偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr"/>
+      <c r="C56" s="9" t="inlineStr"/>
+      <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="10" t="n">
+        <v>297.38</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局成都市税务局第三稽查局依法查处西藏垦泰商贸有限公司两家成都分公司偷逃黄金首饰消费税案件</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr"/>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="10" t="n">
+        <v>277.19</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局沈阳市税务局第一稽查局联合公安机关依法查处涉税中介沈阳遇知科技服务有限公司及其实际控制人</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr"/>
+      <c r="C58" s="9" t="inlineStr"/>
+      <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="10" t="n">
+        <v>233.99</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>云南省保山市税务局稽查局依法查处一起违规享受小规模纳税人减免增值税政策偷税案件</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr"/>
+      <c r="C59" s="9" t="inlineStr"/>
+      <c r="D59" s="9" t="inlineStr"/>
+      <c r="E59" s="10" t="n">
+        <v>225.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局重庆市税务局第三稽查局依法查处网络主播彭煊之偷税案件</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr"/>
+      <c r="C60" s="9" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr"/>
+      <c r="E60" s="10" t="n">
+        <v>216.32</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>湖南省常德市警税联合依法查处一起虚开增值税发票案件</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr"/>
+      <c r="E61" s="10" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局苏州工业园区税务局稽查局依法查处力软信息技术（苏州）有限公司骗享小微企业税收优惠偷税案件</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>78.27</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr"/>
+      <c r="D62" s="9" t="inlineStr"/>
+      <c r="E62" s="10" t="n">
+        <v>177.57</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局青岛市税务局第一稽查局依法查处市南区尚品优食品店直播销售偷税案件</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr"/>
+      <c r="C63" s="9" t="inlineStr"/>
+      <c r="D63" s="9" t="inlineStr"/>
+      <c r="E63" s="10" t="n">
+        <v>177.12</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局宿迁市税务局稽查局依法查处自然人王建军偷税案件</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>81.14</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr"/>
+      <c r="D64" s="9" t="inlineStr"/>
+      <c r="E64" s="10" t="n">
+        <v>162.33</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局厦门市税务局第二稽查局依法查处厦门星曜贸易有限公司隐匿未开票收入偷税案件</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="10" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>湖北省警税联合依法查处一起虚开增值税专用发票案件</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr"/>
+      <c r="D66" s="9" t="inlineStr"/>
+      <c r="E66" s="10" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局阿拉尔税务局稽查局依法查处宏润运输有限公司拆分经营骗享小规模纳税人税费优惠偷税案件</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr"/>
+      <c r="C67" s="9" t="inlineStr"/>
+      <c r="D67" s="9" t="inlineStr"/>
+      <c r="E67" s="10" t="n">
+        <v>142.31</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局赤峰市税务局第一稽查局依法查处网络主播郭鑫鑫偷税案件</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr"/>
+      <c r="C68" s="9" t="inlineStr"/>
+      <c r="D68" s="9" t="inlineStr"/>
+      <c r="E68" s="10" t="n">
+        <v>141.01</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局佛山市税务局第一稽查局依法查处佛山海中金进出口有限公司虚假申报出口应征税货物收入偷税案件</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="10" t="n">
+        <v>125.24</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局厦门市税务局第一稽查局依法对网络主播程虎偷税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr"/>
+      <c r="C70" s="9" t="inlineStr"/>
+      <c r="D70" s="9" t="inlineStr"/>
+      <c r="E70" s="10" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局大连市税务局第三稽查局依法查处自然人王充少缴税款案件</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr"/>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="10" t="n">
+        <v>116.61</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局常州市税务局第一稽查局依法查处常州以马内利塑业有限公司网店销售偷税案件</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr"/>
+      <c r="C72" s="9" t="inlineStr"/>
+      <c r="D72" s="9" t="inlineStr"/>
+      <c r="E72" s="10" t="n">
+        <v>101.67</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>甘肃省天水市税务局稽查局依法对网络主播杨天奇偷税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="10" t="n">
+        <v>82.31999999999999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局宁波市税务局稽查局依法查处涉税中介宁波甬九财税服务有限公司及其实际控制人凌珊帮助所代理企</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="D74" s="9" t="inlineStr"/>
+      <c r="E74" s="10" t="n">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>湖北省武汉市税务局稽查局依法对财税中介人员李薇偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="10" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>厦门市税务局稽查局依法对影视制片人栾慧青偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr"/>
+      <c r="D76" s="9" t="inlineStr"/>
+      <c r="E76" s="10" t="n">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局吉林市税务局稽查局联合公安机关依法查处涉税中介吉林市弘成财务咨询服务有限公司及其实际控制</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr"/>
+      <c r="D77" s="9" t="inlineStr"/>
+      <c r="E77" s="10" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>内蒙古自治区呼伦贝尔市税务局稽查局依法对网络主播周梦妮偷税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr"/>
+      <c r="D78" s="9" t="inlineStr"/>
+      <c r="E78" s="10" t="n">
+        <v>25.21</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局广元市税务局稽查局联合公安机关依法查处涉税中介广元市铭慧企业管理有限公司及其实际控制人梁</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr"/>
+      <c r="C79" s="9" t="inlineStr"/>
+      <c r="D79" s="9" t="inlineStr"/>
+      <c r="E79" s="10" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>国家税务总局上海市税务局第一稽查局依法查处涉税中介上海账一财税咨询有限公司操控空壳企业实施违法策划导</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="n">
+        <v>484.39</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="10" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>西安市税务局第三稽查局依法对网络主播贾亚亚、加婵婵偷逃税案件进行处理</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr"/>
+      <c r="D81" s="9" t="inlineStr"/>
+      <c r="E81" s="10" t="n">
+        <v>17.67</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>福建省龙岩市税务局第二稽查局联合法院强制执行一起未依法办理个人所得税综合所得汇算清缴补税案件</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="10" t="n">
+        <v>16.64</v>
       </c>
     </row>
   </sheetData>
